--- a/skills_refined.xlsx
+++ b/skills_refined.xlsx
@@ -732,7 +732,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Academic Integrity Behaviour Identification</t>
+          <t>Academic Integrity Identification</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>academic integrity; honesty; ethical conduct; honor code; behaviour</t>
+          <t>academic integrity; honesty; ethical conduct; honor code; behaviours</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>keep:0, "Academic Integrity Behaviour Identification/Academic Integrity Identification":3</t>
+          <t>keep:0, "Academic Integrity Identification":3</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>academic integrity; ethical standards; honor code; acceptable and unacceptable behaviours; behaviour</t>
+          <t>academic integrity; honour code; misconduct detection; behaviour; acceptable behaviours</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>academic integrity; application; compliance; moral reasoning; decision making</t>
+          <t>academic integrity; research ethics; compliance; moral reasoning; decision making</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>keep:0, "Academic Integrity Application/Academic Integrity Strategy Application":3</t>
+          <t>keep:0, "Academic Integrity Application":3</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="Y5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="b">
         <v>1</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Trust Application</t>
+          <t>Responsibility Application</t>
         </is>
       </c>
       <c r="AB6" t="b">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Support Referral Identification</t>
+          <t>Harm Support Referral Identification</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>crisis intervention; counseling services; referral pathways; victim support resources; self support resources</t>
+          <t>crisis intervention; counseling services; referral pathways; victim support resources; harm</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1432,19 +1432,15 @@
         </is>
       </c>
       <c r="R7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>keep:1, "Support Referral Identification":2</t>
+          <t>keep:2, "Support Referral Identification":1</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1461,7 +1457,7 @@
         </is>
       </c>
       <c r="Y7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="b">
         <v>1</v>
@@ -1803,7 +1799,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>healthy relationships; respectful relationships; relationship characteristics; boundaries; consent</t>
+          <t>healthy relationships; respectful relationships; characteristics; boundaries; consent</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1906,7 +1902,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Academic Integrity Values Application</t>
+          <t>Responsibility Application</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1937,7 +1933,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>academic integrity; ethics; accountability; responsibility; values</t>
+          <t>academic integrity; ethics; accountability; responsibility; application</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1952,19 +1948,15 @@
         </is>
       </c>
       <c r="R11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>keep:1, "Academic Integrity Values Application":2</t>
+          <t>keep:2, "Academic Integrity Values Application":1</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1981,14 +1973,14 @@
         </is>
       </c>
       <c r="Y11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="b">
         <v>1</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Academic Integrity Application</t>
+          <t>Trust Application</t>
         </is>
       </c>
       <c r="AB11" t="b">
@@ -2071,7 +2063,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>healthy relationships; respectful interaction; boundaries and consent; characteristics; safe relationships</t>
+          <t>healthy relationships; respectful interaction; boundaries and consent; interpersonal dynamics; safe respectful relationships</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2089,12 +2081,12 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>keep:2, "Respectful Relationship Characteristics Identification":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -2215,12 +2207,12 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Support Resource Identification":1</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -2350,7 +2342,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>keep:1, "Support Resource Identification/Support Identification":2</t>
+          <t>keep:1, "Support Resource Identification/Support Seeking Identification":2</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -2374,7 +2366,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Harm Support Identification</t>
+          <t>Harm Support Referral Identification</t>
         </is>
       </c>
       <c r="AB14" t="b">
@@ -2475,12 +2467,12 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Academic Integrity Trust Application":1</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2961,7 +2953,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>algorithmic thinking; formal logic; computational thinking; programming concepts; syntax</t>
+          <t>algorithmic thinking; formal logic; computational thinking; programming concepts; program</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2979,12 +2971,12 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>keep:2, "Program Explanation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -3308,7 +3300,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Portfolio Quality Analysis</t>
+          <t>Portfolio Artefact Evaluation</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3339,7 +3331,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>portfolio assessment; artefact evaluation; reflective analysis; quality; e‑portfolio review</t>
+          <t>portfolio assessment; artefact evaluation; reflective analysis; e‑portfolio review; critique</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -3354,15 +3346,19 @@
         </is>
       </c>
       <c r="R22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T22" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>keep:2, "Portfolio Artefact Evaluation":1</t>
+          <t>keep:1, "Portfolio Artefact Evaluation/Portfolio Quality Evaluation":2</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -3379,7 +3375,7 @@
         </is>
       </c>
       <c r="Y22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="b">
         <v>0</v>
@@ -3744,7 +3740,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>keep:0, "Program Explanation/Program Structure Explanation":3</t>
+          <t>keep:0, "Program Structure Explanation/Program Explanation":3</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3847,7 +3843,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>security issues; cybersecurity; vulnerability assessment; risk management; security best practices</t>
+          <t>software; cybersecurity; vulnerability assessment; risk management; security best practices</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -3865,12 +3861,12 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>keep:1, "Security Familiarisation":1, "Security Awareness Development":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3887,7 +3883,7 @@
         </is>
       </c>
       <c r="Y26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="b">
         <v>0</v>
@@ -3973,7 +3969,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>procedural programming; control structures; structured programming; fundamentals; learning</t>
+          <t>fundamentals; learning; structured programming; control structures; procedural programming</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -4496,7 +4492,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>microcontroller; firmware development; PCB design; prototyping; embedded system</t>
+          <t>microcontroller; firmware development; embedded system; Arduino; prototyping</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -4514,12 +4510,12 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr">
         <is>
-          <t>keep:2, "Microcontroller System Prototyping":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -4645,12 +4641,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>keep:0, "Computer System Elements Description":3</t>
+          <t>keep:1, "Computer System Elements Description":2</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -4727,7 +4723,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>IT Professional Characteristics Identification</t>
+          <t>IT Professional Competency Identification</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4758,7 +4754,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>IT competency frameworks; professional standards; role expectations; characteristics; information technology professionals</t>
+          <t>IT competency frameworks; professional standards; ethical guidelines; role expectations; characteristics</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -4773,19 +4769,15 @@
         </is>
       </c>
       <c r="R33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
-          <t>keep:1, "IT Professional Characteristics Identification":2</t>
+          <t>keep:2, "IT Professional Characteristics Identification":1</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -4802,7 +4794,7 @@
         </is>
       </c>
       <c r="Y33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="b">
         <v>0</v>
@@ -4985,7 +4977,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Learning Resource Acquisition</t>
+          <t>Learning Resource Utilisation</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5016,7 +5008,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>information literacy; research skills; digital libraries; learning resources; resource acquisition</t>
+          <t>information literacy; digital libraries; e‑learning platforms; learning resources; resource utilisation</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -5031,19 +5023,15 @@
         </is>
       </c>
       <c r="R35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
-          <t>keep:0, "Learning Resource Acquisition":3</t>
+          <t>keep:2, "Learning Resource Acquisition":1</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -5419,12 +5407,12 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Unix System Configuration":1</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -5448,7 +5436,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>Computing System Construction (LLM verified, sim=0.66)</t>
+          <t>Unix System Configuration</t>
         </is>
       </c>
       <c r="AB38" t="b">
@@ -5506,7 +5494,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Engages with computer system evolution on emerging technology trends.</t>
+          <t>Engages with computer system evolution in the context of emerging technology trends.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5628,7 +5616,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Computer System Configuration</t>
+          <t>Unix System Configuration</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5659,7 +5647,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Unix; Linux; system administration; configuration management; computer systems</t>
+          <t>Unix; Linux; system administration; shell scripting; configuration management</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -5674,19 +5662,15 @@
         </is>
       </c>
       <c r="R40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
-          <t>keep:1, "Computer System Configuration":2</t>
+          <t>keep:2, "Computer System Configuration":1</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -5703,16 +5687,12 @@
         </is>
       </c>
       <c r="Y40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>Computer System Configuration</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="b">
         <v>0</v>
       </c>
@@ -5888,7 +5868,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Attack Impact-countermeasure Assessment</t>
+          <t>Attack Impact Assessment</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5919,7 +5899,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>attack; vulnerability assessment; security controls effectiveness; impact analysis; countermeasure</t>
+          <t>attack; threat modeling; vulnerability assessment; security controls effectiveness; impact analysis</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -5934,19 +5914,15 @@
         </is>
       </c>
       <c r="R42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
-          <t>keep:1, "Attack Impact-Countermeasure Assessment":2</t>
+          <t>keep:2, "Attack Countermeasure Effectiveness Assessment":1</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -5963,7 +5939,7 @@
         </is>
       </c>
       <c r="Y42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="b">
         <v>0</v>
@@ -6018,7 +5994,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cyber-attack Case Study Analysis</t>
+          <t>Case Study Analysis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6049,7 +6025,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>cybersecurity; incident response; threat analysis; cyber attack; case studies</t>
+          <t>cybersecurity; incident response; threat analysis; cyber forensics; case studies</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -6064,19 +6040,15 @@
         </is>
       </c>
       <c r="R43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr">
         <is>
-          <t>keep:1, "Cyber-Attack Case Study Analysis":2</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -6093,16 +6065,12 @@
         </is>
       </c>
       <c r="Y43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>Cyber Attack Handling (LLM verified, sim=0.78)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="b">
         <v>0</v>
       </c>
@@ -6152,7 +6120,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cryptography Approach Explanation</t>
+          <t>Cryptography Application Explanation</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6183,7 +6151,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>encryption algorithms; public key infrastructure; TLS/SSL protocols; cryptographic key management; cryptography approach</t>
+          <t>encryption algorithms; public key infrastructure; TLS/SSL protocols; cryptographic key management; cryptography application</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -6198,19 +6166,15 @@
         </is>
       </c>
       <c r="R44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
-          <t>keep:1, "Cryptography Approach Explanation/Cryptography Explanation":2</t>
+          <t>keep:2, "Cryptography Approach Explanation":1</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -6331,12 +6295,12 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.95</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
-          <t>keep:2, "Cyber Attack Mitigation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -6356,9 +6320,13 @@
         <v>0</v>
       </c>
       <c r="Z45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA45" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>Case Study Analysis (LLM verified, sim=0.78)</t>
+        </is>
+      </c>
       <c r="AB45" t="b">
         <v>0</v>
       </c>
@@ -6439,7 +6407,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>information security; risk assessment; cyber security fundamentals; real world practices; case studies</t>
+          <t>information security; threat modeling; risk assessment; cyber security fundamentals; real world practices</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -6587,7 +6555,7 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
@@ -6717,12 +6685,12 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Network Risk Concept Exploration":1</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -7099,12 +7067,12 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
-          <t>keep:2, "Cyber Security Tool Selection":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -7436,7 +7404,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Discrete Mathematics Application</t>
+          <t>Discrete Mathematics Tools Application</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -7467,7 +7435,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>discrete mathematics; complexity analysis; application; algorithm design; computational theory</t>
+          <t>discrete mathematics; complexity analysis; algorithm design; computational theory; mathematical tools</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -7482,15 +7450,19 @@
         </is>
       </c>
       <c r="R54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S54" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T54" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>keep:2, "Discrete Mathematics Tools Application":1</t>
+          <t>keep:0, "Discrete Mathematics Tool Application/Discrete Mathematics Tools Application":3</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -7507,7 +7479,7 @@
         </is>
       </c>
       <c r="Y54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z54" t="b">
         <v>0</v>
@@ -7737,12 +7709,12 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Discrete Mathematics Foundations Exploration":1</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -7868,7 +7840,7 @@
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr">
         <is>
-          <t>keep:2, "Graph Theory Understanding":1</t>
+          <t>keep:2, "Graph Theory Exploration":1</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -7888,13 +7860,9 @@
         <v>1</v>
       </c>
       <c r="Z57" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>Set Theory Application</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="b">
         <v>0</v>
       </c>
@@ -7993,12 +7961,12 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr">
         <is>
-          <t>keep:2, "Learning Resource Utilisation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -8101,7 +8069,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>analytic number theory; prime distribution; modular arithmetic; Diophantine equations; number theory</t>
+          <t>analytic number theory; prime distribution; modular arithmetic; Diophantine equations; mathematical proofs</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -8123,12 +8091,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>keep:1, "Number Theory Exploration":2</t>
+          <t>keep:0, "Number Theory Exploration":3</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -8145,7 +8113,7 @@
         </is>
       </c>
       <c r="Y59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="b">
         <v>0</v>
@@ -8249,12 +8217,12 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0.95</v>
+        <v>0.925</v>
       </c>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr">
         <is>
-          <t>keep:1, "Predicate Logic Application":1, "Predicate Logic Analysis":1</t>
+          <t>keep:2, "Predicate Logic Application":1</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -8357,7 +8325,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>formal logic; logical inference; truth tables; propositional logic; logic application</t>
+          <t>formal logic; logical inference; truth tables; propositional logic; application</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -8384,7 +8352,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>keep:0, "Propositional Logic Application":2, "Propositional Logic Exploration":1</t>
+          <t>keep:1, "Propositional Logic Application":2</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -8456,7 +8424,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Recurrence Application</t>
+          <t>Recurrence Understanding</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -8505,16 +8473,16 @@
         <v>1</v>
       </c>
       <c r="S62" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>keep:0, "Recurrence Application":3</t>
+          <t>keep:0, "Recurrence Understanding":2, "Recurrence Application":1</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -8534,13 +8502,9 @@
         <v>0</v>
       </c>
       <c r="Z62" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>Combinatorics Application</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="b">
         <v>0</v>
       </c>
@@ -8639,12 +8603,12 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr">
         <is>
-          <t>keep:2, "Set Application":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -8664,9 +8628,13 @@
         <v>0</v>
       </c>
       <c r="Z63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA63" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>Graph Theory Application</t>
+        </is>
+      </c>
       <c r="AB63" t="b">
         <v>0</v>
       </c>
@@ -8842,7 +8810,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Problem Solving</t>
+          <t>Problem Solving Strategy Development</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -8888,15 +8856,19 @@
         </is>
       </c>
       <c r="R65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S65" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T65" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>keep:1, "Problem Solving Strategy Design":1, "Problem Solving Strategy Development":1</t>
+          <t>keep:0, "Problem Solving Strategy Development":2, "Problem-Solving Strategy Development":1</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -9017,12 +8989,12 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "Network Architecture Assessment":1, "Network Construction Review":1</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -9147,12 +9119,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>keep:0, "Network Data Flow Explanation/Data Flow Explanation":3</t>
+          <t>keep:1, "Network Data Flow Explanation/Data Flow Explanation":2</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -9224,12 +9196,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Network Programming Development</t>
+          <t>Network Program Development</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Designs, develops, implements and analyses software across protocol stack layers to enable network interactions.</t>
+          <t>Designs and implements software across protocol stack layers for network interactions.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -9270,15 +9242,19 @@
         </is>
       </c>
       <c r="R68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S68" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T68" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>keep:2, "Network Program Development":1</t>
+          <t>keep:0, "Network Program Development":3</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -9408,7 +9384,7 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>keep:0, "Network Protocol Explanation":2, "Network Protocol Stack Understanding":1</t>
+          <t>keep:1, "Network Protocol Explanation":2</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -9511,7 +9487,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>OSI model; TCP/IP layers; protocol encapsulation; network abstraction; network protocol stack</t>
+          <t>OSI model; TCP/IP layers; network abstraction; network protocol stack; explanation</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -9551,7 +9527,7 @@
         </is>
       </c>
       <c r="Y70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z70" t="b">
         <v>0</v>
@@ -9763,7 +9739,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>cybersecurity; intrusion detection; packet analysis; network issues; network analysis</t>
+          <t>cybersecurity; intrusion detection; packet analysis; vulnerability assessment; network issues</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -9803,12 +9779,16 @@
         </is>
       </c>
       <c r="Y72" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z72" t="b">
         <v>1</v>
       </c>
-      <c r="Z72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>Network Data Analysis (LLM verified, sim=0.62)</t>
+        </is>
+      </c>
       <c r="AB72" t="b">
         <v>0</v>
       </c>
@@ -9858,7 +9838,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Network Solution Provision</t>
+          <t>Network Solution Design</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -9904,19 +9884,15 @@
         </is>
       </c>
       <c r="R73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr">
         <is>
-          <t>keep:1, "Network Solution Provision":2</t>
+          <t>keep:2, "Network Solution Development":1</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -10114,7 +10090,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Protocol Implementation</t>
+          <t>Protocol Implementation Analysis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -10160,19 +10136,15 @@
         </is>
       </c>
       <c r="R75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr">
         <is>
-          <t>keep:1, "Protocol Implementation":2</t>
+          <t>keep:2, "Protocol Implementation":1</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -10293,16 +10265,16 @@
         <v>1</v>
       </c>
       <c r="S76" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t>MIS re-refinement: Structure Rule 1 — tail 'Critique' is not an action-as-noun; rewrite to end in an action.</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>keep:0, "Network Construction Evaluation":2, "Network Construction Critiquing":1</t>
+          <t>keep:0, "Network Construction Review":1, "Network Construction Assessment":1, "Network Construction Evaluation":1</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -10330,9 +10302,13 @@
       </c>
       <c r="AC76" t="inlineStr"/>
       <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>Structure Rule 1 — tail 'Critique' is not an action-as-noun; rewrite to end in an action.</t>
+        </is>
+      </c>
       <c r="AF76" t="b">
         <v>0</v>
       </c>
@@ -10428,7 +10404,7 @@
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr">
         <is>
-          <t>keep:2, "Cloud API Security Application":1</t>
+          <t>keep:2, "Cloud API Security Configuration":1</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -10448,13 +10424,9 @@
         <v>0</v>
       </c>
       <c r="Z77" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>Secure Database Design</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA77" t="inlineStr"/>
       <c r="AB77" t="b">
         <v>0</v>
       </c>
@@ -10504,7 +10476,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Code and Design Analysis</t>
+          <t>Program Code Analysis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -10535,7 +10507,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>static code analysis; software security; secure coding practices; program code; design documentation</t>
+          <t>static code analysis; software security; secure coding practices; OWASP guidelines; program code</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -10550,19 +10522,15 @@
         </is>
       </c>
       <c r="R78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr">
         <is>
-          <t>keep:0, "Code and Design Analysis/Program Code Design Analysis":2, "Program Code Documentation Analysis":1</t>
+          <t>keep:0, "Code Design Analysis":1, "Program Code-Documentation Analysis":1, "Programming Problems Identification":1</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -10579,7 +10547,7 @@
         </is>
       </c>
       <c r="Y78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="b">
         <v>0</v>
@@ -10634,7 +10602,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Data Validation Testing</t>
+          <t>Data Validation Implementation</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -10665,7 +10633,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>software security tools; data integrity checks; validation frameworks; automated testing; quality assurance</t>
+          <t>software security tools; data validation; validation frameworks; automated testing; data integrity checks</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -10680,15 +10648,19 @@
         </is>
       </c>
       <c r="R79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S79" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>keep:0, "Data Validation Tool Utilisation":1, "Data Validation Tool Adoption":1, "Data Validation Tool Implementation":1</t>
+          <t>keep:1, "Data Validation Implementation":2</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -10705,7 +10677,7 @@
         </is>
       </c>
       <c r="Y79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z79" t="b">
         <v>0</v>
@@ -11069,12 +11041,12 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>keep:1, "Programming Issue Mitigation/Program Issue Mitigation":2</t>
+          <t>keep:0, "Programming Issue Mitigation":3</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -11195,12 +11167,12 @@
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Secure Coding Principles Explanation":1</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -11220,9 +11192,13 @@
         <v>0</v>
       </c>
       <c r="Z83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA83" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>Secure Coding Principle Explanation (LLM verified, sim=0.68)</t>
+        </is>
+      </c>
       <c r="AB83" t="b">
         <v>0</v>
       </c>
@@ -11277,7 +11253,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Secure CD pipelines integrating automated testing, vulnerability scanning, and compliance checks.</t>
+          <t>Secure CD pipelines with automated testing, vulnerability scanning, and compliance checks.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -11398,7 +11374,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Secure Database Design</t>
+          <t>Database Security Planning</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -11429,7 +11405,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>encryption; access control; database; secure; design</t>
+          <t>encryption; access control; database; design; cloud API security</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -11444,15 +11420,19 @@
         </is>
       </c>
       <c r="R85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S85" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T85" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>keep:2, "Database Security Planning":1</t>
+          <t>keep:0, "Database Security Planning":2, "Secure Database Designing":1</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -11469,12 +11449,16 @@
         </is>
       </c>
       <c r="Y85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA85" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>Cloud API Security Implementation</t>
+        </is>
+      </c>
       <c r="AB85" t="b">
         <v>0</v>
       </c>
@@ -11524,7 +11508,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Secure Software Design Application</t>
+          <t>Secure Software Design</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -11570,19 +11554,15 @@
         </is>
       </c>
       <c r="R86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr">
         <is>
-          <t>keep:0, "Secure Software Design Application/Software Design Security Application":3</t>
+          <t>keep:0, "Secure Coding Application":1, "Secure Software Design Application":1, "Software Design Security Implementation":1</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -11654,7 +11634,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Secure Coding Principles Explanation</t>
+          <t>Secure Coding Principle Explanation</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -11685,7 +11665,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>secure coding; threat modeling; vulnerability assessment; principle; explanation</t>
+          <t>secure coding; threat modelling; vulnerability assessment; principle; explanation</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -11700,19 +11680,15 @@
         </is>
       </c>
       <c r="R87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr">
         <is>
-          <t>keep:1, "Secure Coding Principles Explanation":2</t>
+          <t>keep:2, "Secure Coding Principles Explanation":1</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -11732,13 +11708,9 @@
         <v>1</v>
       </c>
       <c r="Z87" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>Secure Coding Principles Presentation (LLM verified, sim=0.68)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA87" t="inlineStr"/>
       <c r="AB87" t="b">
         <v>0</v>
       </c>
@@ -11914,7 +11886,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Secure Coding Explanation</t>
+          <t>Secure Coding Principles Explanation</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -11945,7 +11917,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>secure coding principles; technical writing; audience tailoring; cybersecurity communication; secure coding explanation</t>
+          <t>secure coding principles; technical writing; audience tailoring; cybersecurity communication; code review facilitation</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -11972,7 +11944,7 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>keep:0, "Secure Coding Explanation/Secure Coding Principles Explanation":3</t>
+          <t>keep:0, "Secure Coding Principles Explanation/Secure Coding Explanation/Secure Coding Principle Explanation":3</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -11989,7 +11961,7 @@
         </is>
       </c>
       <c r="Y89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="b">
         <v>1</v>
@@ -12205,7 +12177,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>scrum; JIRA; agile; project management; engagement</t>
+          <t>scrum; sprint planning; agile; project management; engagement</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -12353,12 +12325,12 @@
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr">
         <is>
-          <t>keep:2, "Career Plan Development":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -12610,7 +12582,7 @@
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr">
         <is>
-          <t>keep:2, "Skills Development":1</t>
+          <t>keep:2, "Skill Development":1</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -12682,7 +12654,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cybersecurity Evaluation</t>
+          <t>Cybersecurity Risk Assessment</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -12713,7 +12685,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>threat modeling; vulnerability assessment; risk management; cybersecurity; regulatory requirements</t>
+          <t>threat modeling; vulnerability assessment; risk management; NIST framework; cybersecurity</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -12728,19 +12700,15 @@
         </is>
       </c>
       <c r="R95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr">
         <is>
-          <t>keep:0, "Cybersecurity Evaluation":2, "Cybersecurity Review":1</t>
+          <t>keep:0, "Cybersecurity Assessment":1, "Cybersecurity Evaluation":1, "Risk Assessment":1</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
@@ -12757,7 +12725,7 @@
         </is>
       </c>
       <c r="Y95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="b">
         <v>0</v>
@@ -12817,7 +12785,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Engages with CI/CD pipelines using tools across builds, tests, and deployments.</t>
+          <t>Engages with CI/CD pipelines using tools.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -12843,7 +12811,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>CI/CD; Jenkins; Kubernetes; processes; practices</t>
+          <t>CI/CD; Jenkins; Kubernetes; devops pipeline; processes</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -12947,7 +12915,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Focuses on gender equity principles in IT curricula to ensure leaders are well placed to address these challenges.</t>
+          <t>Focuses on gender equity principles in IT curricula to ensure leaders' inclusive technology.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -12991,12 +12959,12 @@
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr">
         <is>
-          <t>keep:2, "Gender-Equity Diversity Education":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
@@ -13117,12 +13085,12 @@
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr">
         <is>
-          <t>keep:2, "IT Ethical Consideration Evaluation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
@@ -13225,7 +13193,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>indigenous knowledge; integration; community engagement; traditional ecological knowledge; indigenous perspective</t>
+          <t>indigenous knowledge; community engagement; traditional ecological knowledge; indigenous perspective; integration</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -13369,12 +13337,12 @@
         <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.925</v>
       </c>
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Leadership Style Impact Reflection":1</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
@@ -13394,13 +13362,9 @@
         <v>0</v>
       </c>
       <c r="Z100" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>Leadership Style Analysis (LLM verified, sim=0.67)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA100" t="inlineStr"/>
       <c r="AB100" t="b">
         <v>0</v>
       </c>
@@ -13576,12 +13540,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Professional Collaboration</t>
+          <t>Professional Teamwork Collaboration</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>In hybrid IT teams, professional ethics and behaviours are engaged.</t>
+          <t>In hybrid IT teams, professional ethics and behaviours engage.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -13607,7 +13571,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>IT collaboration; ethical standards; teamwork; professional; professional behaviours</t>
+          <t>IT collaboration; team dynamics; ethical standards; teamwork; professional</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -13622,19 +13586,15 @@
         </is>
       </c>
       <c r="R102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="T102" t="inlineStr"/>
       <c r="U102" t="inlineStr">
         <is>
-          <t>keep:0, "Professional Collaboration/Professional Relationships Collaboration":2, "Teamwork Collaboration":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -13651,7 +13611,7 @@
         </is>
       </c>
       <c r="Y102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="b">
         <v>0</v>
@@ -13755,12 +13715,12 @@
         <v>0</v>
       </c>
       <c r="S103" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T103" t="inlineStr"/>
       <c r="U103" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Regulatory Standards Evaluation":1</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
@@ -14084,7 +14044,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Leadership Style Analysis</t>
+          <t>Leadership Style Impact Observation</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -14115,7 +14075,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>leadership styles; organisational structures; communication practices; conflict management approaches; professional relationships</t>
+          <t>leadership styles; communication practices; conflict management approaches; professional relationships; impact observation</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -14130,15 +14090,19 @@
         </is>
       </c>
       <c r="R106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S106" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T106" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>keep:2, "Leadership Style Impact Observation":1</t>
+          <t>keep:1, "Leadership Style Impact Observation":2</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
@@ -14155,12 +14119,16 @@
         </is>
       </c>
       <c r="Y106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z106" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA106" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>Leadership Style Impact Observation</t>
+        </is>
+      </c>
       <c r="AB106" t="b">
         <v>0</v>
       </c>
@@ -14519,7 +14487,7 @@
       <c r="T109" t="inlineStr"/>
       <c r="U109" t="inlineStr">
         <is>
-          <t>keep:1, "Code Tracing Debugging":1, "Code Tracing-Debugging Application":1</t>
+          <t>keep:2, "Code Tracing Debugging Application":1</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
@@ -14592,7 +14560,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Solution Structure Communication</t>
+          <t>Solution Diagram Communication</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -14623,7 +14591,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>solution structures; solution architecture; UML diagrams; flowcharting; technical documentation</t>
+          <t>visual communication; solution architecture; UML diagrams; flowcharting; technical documentation</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -14638,19 +14606,15 @@
         </is>
       </c>
       <c r="R110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T110" t="inlineStr"/>
       <c r="U110" t="inlineStr">
         <is>
-          <t>keep:1, "Solution Structure Communication":2</t>
+          <t>keep:2, "Solution Structure Communication":1</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
@@ -14667,7 +14631,7 @@
         </is>
       </c>
       <c r="Y110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="b">
         <v>1</v>
@@ -14863,7 +14827,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Applies and explains OOP principles—abstraction, encapsulation, inheritance, polymorphism—in documentation and code.</t>
+          <t>Applies and explains OOP principles—abstraction, encapsulation, inheritance, polymorphism—in design documentation and code reviews.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -14912,7 +14876,7 @@
       <c r="T112" t="inlineStr"/>
       <c r="U112" t="inlineStr">
         <is>
-          <t>keep:2, "Object-Oriented Principles Application":1</t>
+          <t>keep:2, "Object-oriented Principles Application Explanation":1</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
@@ -14921,7 +14885,7 @@
         </is>
       </c>
       <c r="W112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X112" t="inlineStr">
         <is>
@@ -15165,12 +15129,12 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>keep:0, "Code Tracing Debugging":3</t>
+          <t>keep:0, "Code Tracing Debugging/Code Debugging":2, "Code Issue Identification":1</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
@@ -15374,7 +15338,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Object-oriented Program Testing</t>
+          <t>Program Implementation Testing</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -15432,7 +15396,7 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>keep:0, "Object-Oriented Program Testing/Object-Oriented Program Implementation Testing/Program Implementation Testing":3</t>
+          <t>keep:0, "Program Implementation Testing/Program Testing":3</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
@@ -15632,7 +15596,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Solution Structure Development</t>
+          <t>Solution Structure Design</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -15663,7 +15627,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>technical writing; system diagrams; UML; evaluation; solution structure</t>
+          <t>technical writing; system diagrams; UML; design; solution structure</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -15690,7 +15654,7 @@
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>keep:1, "Solution Structure Development":2</t>
+          <t>keep:0, "Solution Structure Design":2, "Solution Structure Design Evaluation":1</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
@@ -15714,7 +15678,7 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>Solution Structure Development</t>
+          <t>Solution Diagram Communication</t>
         </is>
       </c>
       <c r="AB118" t="b">
@@ -15820,7 +15784,7 @@
       <c r="T119" t="inlineStr"/>
       <c r="U119" t="inlineStr">
         <is>
-          <t>keep:2, "Authentication Mechanism Utilisation":1</t>
+          <t>keep:1, "Authentication Mechanism Utilisation":1, "Authentication Mechanism Acquisition":1</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
@@ -15941,12 +15905,12 @@
         <v>0</v>
       </c>
       <c r="S120" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T120" t="inlineStr"/>
       <c r="U120" t="inlineStr">
         <is>
-          <t>keep:2, "Cyber Crime Forensic Investigation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
@@ -15966,9 +15930,13 @@
         <v>0</v>
       </c>
       <c r="Z120" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA120" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>Forensic Data Analysis (LLM verified, sim=0.66)</t>
+        </is>
+      </c>
       <c r="AB120" t="b">
         <v>0</v>
       </c>
@@ -16305,7 +16273,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>exploitation techniques; authentication mechanisms; Windows registry forensics; digital evidence acquisition; exploitation technique application</t>
+          <t>exploitation techniques; authentication mechanisms; Windows registry forensics; digital evidence acquisition; application</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -16327,12 +16295,12 @@
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>keep:0, "Exploitation Technique Application":3</t>
+          <t>keep:0, "Exploitation Technique Application":2, "Digital Evidence Acquisition":1</t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
@@ -16356,7 +16324,7 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>Cyber Crime Investigation (LLM verified, sim=0.61)</t>
+          <t>Authentication Mechanism Investigation (LLM verified, sim=0.70)</t>
         </is>
       </c>
       <c r="AB123" t="b">
@@ -16482,13 +16450,9 @@
         <v>0</v>
       </c>
       <c r="Z124" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>Cyber Crime Investigation (LLM verified, sim=0.66)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA124" t="inlineStr"/>
       <c r="AB124" t="b">
         <v>0</v>
       </c>
@@ -16569,7 +16533,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>computer forensics; digital investigation; forensic analysis tools; computer forensic frameworks; framework application</t>
+          <t>computer forensics; forensic analysis tools; computer forensic frameworks; application; evidence collection</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -16592,7 +16556,7 @@
       <c r="T125" t="inlineStr"/>
       <c r="U125" t="inlineStr">
         <is>
-          <t>keep:1, "Forensic Framework Discussion":1, "Computer Forensic Framework Application":1</t>
+          <t>keep:1, "Computer Forensic Framework Application":1, "Forensic Framework Discussion":1</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
@@ -16790,7 +16754,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Findings Report Preparation</t>
+          <t>Findings Report Development</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -16821,7 +16785,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>research design; analysis and reporting; stakeholder communication; findings; report</t>
+          <t>research design; data collection methods; analysis and reporting; stakeholder communication; findings</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -16848,7 +16812,7 @@
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>keep:1, "Findings Report Preparation":2</t>
+          <t>keep:0, "Findings Report Development":2, "Findings Report Preparation":1</t>
         </is>
       </c>
       <c r="V127" t="inlineStr">
@@ -16865,16 +16829,12 @@
         </is>
       </c>
       <c r="Y127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z127" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>Forensic Report Preparation (LLM verified, sim=0.76)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA127" t="inlineStr"/>
       <c r="AB127" t="b">
         <v>0</v>
       </c>
@@ -16924,7 +16884,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>IT Law Familiarisation</t>
+          <t>IT Law Compliance Familiarisation</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -16970,19 +16930,15 @@
         </is>
       </c>
       <c r="R128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T128" t="inlineStr"/>
       <c r="U128" t="inlineStr">
         <is>
-          <t>keep:0, "IT Law Familiarisation":3</t>
+          <t>keep:2, "IT Law Familiarisation":1</t>
         </is>
       </c>
       <c r="V128" t="inlineStr">
@@ -17054,7 +17010,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Investigative Findings Communication</t>
+          <t>Forensic Findings Communication</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -17100,15 +17056,19 @@
         </is>
       </c>
       <c r="R129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S129" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="T129" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Forensic Findings Communication/Digital Forensic Communication":2, "Procedures and Findings Communication":1</t>
         </is>
       </c>
       <c r="V129" t="inlineStr">
@@ -17180,7 +17140,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>System Log Analysis</t>
+          <t>System Log Acquisition</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -17211,7 +17171,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>log parsing; digital forensics; SIEM; incident response; syslog</t>
+          <t>log parsing; digital forensics; system log acquisition; incident response; syslog</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -17226,15 +17186,19 @@
         </is>
       </c>
       <c r="R130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S130" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T130" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>keep:2, "System Log Acquisition":1</t>
+          <t>keep:1, "System Log Acquisition":2</t>
         </is>
       </c>
       <c r="V130" t="inlineStr">
@@ -17251,7 +17215,7 @@
         </is>
       </c>
       <c r="Y130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z130" t="b">
         <v>0</v>
@@ -17306,7 +17270,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Forensic Technique Evaluation</t>
+          <t>Forensic Technique Application</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -17337,7 +17301,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>forensic techniques; data recovery; computer crime; access acquisition; application</t>
+          <t>forensic techniques; data recovery; computer crime; access acquisition; contemporary forensic techniques</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -17352,36 +17316,32 @@
         </is>
       </c>
       <c r="R131" t="b">
+        <v>0</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="T131" t="inlineStr"/>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>keep:2, "Forensic Technique Evaluation":1</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Applies contemporary forensic techniques to gain system access and recover computer crime data effectively.</t>
+        </is>
+      </c>
+      <c r="W131" t="b">
+        <v>0</v>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>forensic techniques, data recovery, computer crime, access acquisition, application</t>
+        </is>
+      </c>
+      <c r="Y131" t="b">
         <v>1</v>
-      </c>
-      <c r="S131" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
-      <c r="U131" t="inlineStr">
-        <is>
-          <t>keep:1, "Forensic Technique Evaluation":2</t>
-        </is>
-      </c>
-      <c r="V131" t="inlineStr">
-        <is>
-          <t>Applies contemporary forensic techniques to gain system access and recover computer crime data effectively.</t>
-        </is>
-      </c>
-      <c r="W131" t="b">
-        <v>0</v>
-      </c>
-      <c r="X131" t="inlineStr">
-        <is>
-          <t>forensic techniques, data recovery, computer crime, access acquisition, application</t>
-        </is>
-      </c>
-      <c r="Y131" t="b">
-        <v>0</v>
       </c>
       <c r="Z131" t="b">
         <v>0</v>
@@ -17468,7 +17428,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>personal branding; professional capabilities; employer communication; career aspirations; career articulation</t>
+          <t>professional capabilities; career planning; employer communication; career aspirations; articulation</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -17486,12 +17446,12 @@
         <v>0</v>
       </c>
       <c r="S132" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T132" t="inlineStr"/>
       <c r="U132" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Career Goal Articulation":1</t>
         </is>
       </c>
       <c r="V132" t="inlineStr">
@@ -17638,13 +17598,9 @@
         <v>0</v>
       </c>
       <c r="Z133" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>Critical Self‑assessment (LLM verified, sim=0.61)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA133" t="inlineStr"/>
       <c r="AB133" t="b">
         <v>0</v>
       </c>
@@ -17744,12 +17700,12 @@
         <v>0</v>
       </c>
       <c r="S134" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T134" t="inlineStr"/>
       <c r="U134" t="inlineStr">
         <is>
-          <t>keep:1, "Critical Reflection":1, "Reflective Practice Documentation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V134" t="inlineStr">
@@ -17822,7 +17778,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Career Aspirations Articulation</t>
+          <t>Employer Communication</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -17853,7 +17809,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>personal branding; employer value proposition; professional competencies; aspirations; articulation</t>
+          <t>personal branding; employer value proposition; career networking; professional competencies; job search strategy</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -17868,19 +17824,15 @@
         </is>
       </c>
       <c r="R135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T135" t="inlineStr"/>
       <c r="U135" t="inlineStr">
         <is>
-          <t>keep:1, "Career Aspirations Articulation":2</t>
+          <t>keep:2, "Professional Capabilities Articulation":1</t>
         </is>
       </c>
       <c r="V135" t="inlineStr">
@@ -17897,16 +17849,12 @@
         </is>
       </c>
       <c r="Y135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z135" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA135" t="inlineStr">
-        <is>
-          <t>Career Aspiration Articulation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA135" t="inlineStr"/>
       <c r="AB135" t="b">
         <v>0</v>
       </c>
@@ -17957,7 +17905,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Ethical Professional Practice Demonstration</t>
+          <t>Ethical Work Practice Demonstration</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -17988,7 +17936,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>professional ethics; demonstration; code of conduct; responsible computing; work practice</t>
+          <t>professional ethics; code of conduct; responsible computing; work practice; demonstration</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -18010,12 +17958,12 @@
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>keep:1, "Ethical Professional Practice Demonstration/Ethical Work Practice Demonstration":2</t>
+          <t>keep:0, "Ethical Work Practice Demonstration":3</t>
         </is>
       </c>
       <c r="V136" t="inlineStr">
@@ -18088,7 +18036,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Professional Work Experience Participation</t>
+          <t>Placement Participation</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -18119,7 +18067,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>work‑integrated learning; placement management; industry partnership; professional work experience; participation</t>
+          <t>work‑integrated learning; placement management; industry partnership; student onboarding; participation</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -18134,19 +18082,15 @@
         </is>
       </c>
       <c r="R137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="T137" t="inlineStr"/>
       <c r="U137" t="inlineStr">
         <is>
-          <t>keep:0, "Professional Work Experience Participation":2, "IT Placement Participation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V137" t="inlineStr">
@@ -18163,16 +18107,12 @@
         </is>
       </c>
       <c r="Y137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z137" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA137" t="inlineStr">
-        <is>
-          <t>Work Experience Participation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA137" t="inlineStr"/>
       <c r="AB137" t="b">
         <v>0</v>
       </c>
@@ -18272,12 +18212,12 @@
         <v>0</v>
       </c>
       <c r="S138" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T138" t="inlineStr"/>
       <c r="U138" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Personal Development Planning":1</t>
         </is>
       </c>
       <c r="V138" t="inlineStr">
@@ -18350,7 +18290,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Personal Development Planning</t>
+          <t>Development Planning</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -18381,7 +18321,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>career planning; professional development; goal setting; job search strategy; personal development</t>
+          <t>career planning; professional development; development plans; job search strategy; personal development</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -18396,15 +18336,19 @@
         </is>
       </c>
       <c r="R139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S139" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T139" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>keep:1, "Development Plan Preparation":1, "Development Planning":1</t>
+          <t>keep:0, "Development Planning/Personal‑Professional Development Planning/Personal Professional Development Planning":3</t>
         </is>
       </c>
       <c r="V139" t="inlineStr">
@@ -18421,7 +18365,7 @@
         </is>
       </c>
       <c r="Y139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z139" t="b">
         <v>0</v>
@@ -18508,7 +18452,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>personal branding; employer outreach; relationship building; professional networking; career aspirations</t>
+          <t>personal branding; employer outreach; professional capabilities; relationship building; professional networking</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -18555,9 +18499,13 @@
         <v>1</v>
       </c>
       <c r="Z140" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA140" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>Employer Communication</t>
+        </is>
+      </c>
       <c r="AB140" t="b">
         <v>0</v>
       </c>
@@ -18662,7 +18610,7 @@
       <c r="T141" t="inlineStr"/>
       <c r="U141" t="inlineStr">
         <is>
-          <t>keep:1, "IT Professional Practice Development":1, "Professional Practice Familiarisation":1</t>
+          <t>keep:1, "Professional Practice Learning":1, "Professional Practice Familiarisation":1</t>
         </is>
       </c>
       <c r="V141" t="inlineStr">
@@ -18735,7 +18683,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Work Experience Participation</t>
+          <t>Professional Work Participation</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -18766,7 +18714,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>participation; workplace learning; industry placement; professional work experience; host organization</t>
+          <t>internship; workplace learning; industry placement; professional work experience; participation</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -18793,7 +18741,7 @@
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>keep:1, "Work Experience Participation/Professional Work Experience Participation":2</t>
+          <t>keep:0, "Professional Work Participation":2, "Professional Work Experience Undertaking":1</t>
         </is>
       </c>
       <c r="V142" t="inlineStr">
@@ -18813,9 +18761,13 @@
         <v>1</v>
       </c>
       <c r="Z142" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA142" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>Placement Participation (LLM verified, sim=0.83)</t>
+        </is>
+      </c>
       <c r="AB142" t="b">
         <v>0</v>
       </c>
@@ -18915,12 +18867,12 @@
         <v>0</v>
       </c>
       <c r="S143" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T143" t="inlineStr"/>
       <c r="U143" t="inlineStr">
         <is>
-          <t>keep:2, "Experience and Skills Documentation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V143" t="inlineStr">
@@ -19067,9 +19019,13 @@
         <v>0</v>
       </c>
       <c r="Z144" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA144" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>Anti-reverse Engineering Implementation</t>
+        </is>
+      </c>
       <c r="AB144" t="b">
         <v>0</v>
       </c>
@@ -19252,7 +19208,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Designs and implements assembly modules across multiple processor architectures to produce portable software components.</t>
+          <t>Designs and implements assembly modules across multiple processor architectures for portable software components.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -19409,7 +19365,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>sandbox; static analysis; dynamic analysis; reverse engineering; malware analysis tool</t>
+          <t>utilisation; static analysis; dynamic analysis; reverse engineering; malware analysis tool</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -19449,7 +19405,7 @@
         </is>
       </c>
       <c r="Y147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z147" t="b">
         <v>1</v>
@@ -19558,12 +19514,12 @@
         <v>0</v>
       </c>
       <c r="S148" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T148" t="inlineStr"/>
       <c r="U148" t="inlineStr">
         <is>
-          <t>keep:2, "Malware Classification-Reporting Standards Implementation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V148" t="inlineStr">
@@ -19645,7 +19601,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Provides a comprehensive overview of malware development literature and detection strategies for academic research.</t>
+          <t>Provides a comprehensive overview of malware development literature and detection strategies.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -19689,12 +19645,12 @@
         <v>0</v>
       </c>
       <c r="S149" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="T149" t="inlineStr"/>
       <c r="U149" t="inlineStr">
         <is>
-          <t>keep:0, "Malware Detection Strategy Documentation":1, "Malware Detection Strategy Description":1, "Malware Detection Strategy Analysis":1</t>
+          <t>keep:1, "Malware Detection Strategy Survey":1, "Malware Detection Strategy Documentation":1</t>
         </is>
       </c>
       <c r="V149" t="inlineStr">
@@ -19703,7 +19659,7 @@
         </is>
       </c>
       <c r="W149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X149" t="inlineStr">
         <is>
@@ -19714,13 +19670,9 @@
         <v>0</v>
       </c>
       <c r="Z149" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA149" t="inlineStr">
-        <is>
-          <t>Malware Understanding (LLM verified, sim=0.64)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA149" t="inlineStr"/>
       <c r="AB149" t="b">
         <v>0</v>
       </c>
@@ -19825,7 +19777,7 @@
       <c r="T150" t="inlineStr"/>
       <c r="U150" t="inlineStr">
         <is>
-          <t>keep:2, "Malware Persistence Detection":1</t>
+          <t>keep:2, "Malware Persistence Detection Implementation":1</t>
         </is>
       </c>
       <c r="V150" t="inlineStr">
@@ -20074,12 +20026,12 @@
         <v>0</v>
       </c>
       <c r="S152" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr">
         <is>
-          <t>keep:2, "Malware Classification Reporting Implementation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V152" t="inlineStr">
@@ -20183,7 +20135,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>cybersecurity; malware analysis; threat intelligence; reverse engineering; understanding malware</t>
+          <t>cybersecurity; malware analysis; threat intelligence; reverse engineering; intrusion detection</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -20205,12 +20157,12 @@
       </c>
       <c r="T153" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>keep:0, "Malware Understanding":2, "Malware Classification":1</t>
+          <t>keep:0, "Malware Understanding":3</t>
         </is>
       </c>
       <c r="V153" t="inlineStr">
@@ -20227,20 +20179,20 @@
         </is>
       </c>
       <c r="Y153" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z153" t="b">
         <v>1</v>
       </c>
-      <c r="Z153" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA153" t="inlineStr"/>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>Malware Detection Strategy Review (LLM verified, sim=0.64)</t>
+        </is>
+      </c>
       <c r="AB153" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>vague skill from course description — "Malware Understanding" uses non-assessable term: {'understanding'}</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC153" t="inlineStr"/>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
@@ -20361,9 +20313,13 @@
         <v>0</v>
       </c>
       <c r="Z154" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA154" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>Anti-reverse Engineering Implementation</t>
+        </is>
+      </c>
       <c r="AB154" t="b">
         <v>0</v>
       </c>
@@ -20414,7 +20370,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Incident Response Attribution Reporting</t>
+          <t>Response Attribution Reporting</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -20445,7 +20401,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>threat intelligence; incident response; mitigation; malware attribution; attack reporting</t>
+          <t>threat intelligence; incident response; malware attribution; attack reporting; mitigation</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -20472,7 +20428,7 @@
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>keep:1, "Incident Response Attribution Reporting":2</t>
+          <t>keep:0, "Response Attribution Reporting":2, "Incident Reporting":1</t>
         </is>
       </c>
       <c r="V155" t="inlineStr">
@@ -20580,7 +20536,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>network forensics; packet analysis; Wireshark; TCPDump; digital evidence</t>
+          <t>network forensics; packet analysis; Wireshark; TCPDump; network forensics tools</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -20620,7 +20576,7 @@
         </is>
       </c>
       <c r="Y156" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z156" t="b">
         <v>0</v>
@@ -20852,12 +20808,12 @@
         <v>0</v>
       </c>
       <c r="S158" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T158" t="inlineStr"/>
       <c r="U158" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Intrusion Detection System Configuration":1</t>
         </is>
       </c>
       <c r="V158" t="inlineStr">
@@ -21233,12 +21189,12 @@
         <v>0</v>
       </c>
       <c r="S161" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T161" t="inlineStr"/>
       <c r="U161" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Network Attack Investigation":1</t>
         </is>
       </c>
       <c r="V161" t="inlineStr">
@@ -21258,13 +21214,9 @@
         <v>0</v>
       </c>
       <c r="Z161" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA161" t="inlineStr">
-        <is>
-          <t>Network Log Recovery Analysis (LLM verified, sim=0.63)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA161" t="inlineStr"/>
       <c r="AB161" t="b">
         <v>0</v>
       </c>
@@ -21389,9 +21341,13 @@
         <v>0</v>
       </c>
       <c r="Z162" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA162" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>Network Forensic Investigation (LLM verified, sim=0.63)</t>
+        </is>
+      </c>
       <c r="AB162" t="b">
         <v>0</v>
       </c>
@@ -21750,7 +21706,7 @@
       <c r="T165" t="inlineStr"/>
       <c r="U165" t="inlineStr">
         <is>
-          <t>keep:2, "Forensic Incident Handling":1</t>
+          <t>keep:1, "Incident Handling":1, "Simulated Incident Response Reporting":1</t>
         </is>
       </c>
       <c r="V165" t="inlineStr">
@@ -21854,7 +21810,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>network forensics; wireless security; packet capture; Wireshark; wireless traffic</t>
+          <t>network forensics; wireless security; packet capture; Wireshark; wireless network traffic</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -22006,12 +21962,12 @@
         <v>0</v>
       </c>
       <c r="S167" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T167" t="inlineStr"/>
       <c r="U167" t="inlineStr">
         <is>
-          <t>keep:2, "Career Objectives Articulation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V167" t="inlineStr">
@@ -22083,7 +22039,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Development Decision-making</t>
+          <t>Personal Professional Development Decision-making</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -22114,7 +22070,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>career planning; goal setting; self-assessment; personal development; decision making</t>
+          <t>career planning; decision-making; goal setting; self-assessment; personal development</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -22136,12 +22092,12 @@
       </c>
       <c r="T168" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>keep:0, "Development Decision-Making/Development Decision-making/Personal Professional Development Decision-making":3</t>
+          <t>keep:1, "Personal Professional Development Decision-making":2</t>
         </is>
       </c>
       <c r="V168" t="inlineStr">
@@ -22262,12 +22218,12 @@
         <v>0</v>
       </c>
       <c r="S169" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T169" t="inlineStr"/>
       <c r="U169" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "IT Competency Documentation":1</t>
         </is>
       </c>
       <c r="V169" t="inlineStr">
@@ -22339,7 +22295,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Professional Role Critical Reflection</t>
+          <t>Critical Professional Role Reflection</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -22370,7 +22326,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>critical reflection; reflective practice; professional ethics; self‑assessment; professional role</t>
+          <t>critical reflection; reflective practice; role; self‑assessment; metacognition</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
@@ -22397,7 +22353,7 @@
       </c>
       <c r="U170" t="inlineStr">
         <is>
-          <t>keep:0, "Professional Role Critical Reflection/Professional Role Reflection":2, "IT Professional Reflecting":1</t>
+          <t>keep:1, "Critical Professional Role Reflection/IT Professional Critical Reflection":2</t>
         </is>
       </c>
       <c r="V170" t="inlineStr">
@@ -22518,12 +22474,12 @@
         <v>0</v>
       </c>
       <c r="S171" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T171" t="inlineStr"/>
       <c r="U171" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Employment Evidence Provision":1</t>
         </is>
       </c>
       <c r="V171" t="inlineStr">
@@ -22595,7 +22551,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Ethical Work Practice Demonstration</t>
+          <t>Ethical Professional Practice Demonstration</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -22626,7 +22582,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>IT ethics; professional conduct; work practice; demonstration; efficient work practices</t>
+          <t>IT ethics; professional conduct; efficient work practices; work practice; demonstration</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -22641,15 +22597,19 @@
         </is>
       </c>
       <c r="R172" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S172" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T172" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>keep:2, "Professional Work Practice Demonstration":1</t>
+          <t>keep:1, "Ethical Professional Practice Demonstration":2</t>
         </is>
       </c>
       <c r="V172" t="inlineStr">
@@ -22721,7 +22681,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Learning Outcomes Demonstration</t>
+          <t>Course Graduate Outcomes Demonstration</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -22752,7 +22712,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>curriculum mapping; learning outcomes assessment; demonstration; graduate; course learning outcomes</t>
+          <t>course; curriculum mapping; learning outcomes assessment; competency-based education; graduate</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
@@ -22774,12 +22734,12 @@
       </c>
       <c r="T173" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U173" t="inlineStr">
         <is>
-          <t>keep:1, "Learning Outcomes Demonstration":2</t>
+          <t>keep:0, "Course Graduate Outcomes Demonstration/Graduate Learning Outcomes Demonstration":3</t>
         </is>
       </c>
       <c r="V173" t="inlineStr">
@@ -23008,7 +22968,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>internship; work-based learning; professional placement; experience; career readiness</t>
+          <t>internship; work-based learning; professional placement; participation; career readiness</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -23026,12 +22986,12 @@
         <v>0</v>
       </c>
       <c r="S175" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T175" t="inlineStr"/>
       <c r="U175" t="inlineStr">
         <is>
-          <t>keep:2, "Placement Participation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V175" t="inlineStr">
@@ -23048,7 +23008,7 @@
         </is>
       </c>
       <c r="Y175" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z175" t="b">
         <v>0</v>
@@ -23103,7 +23063,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Study-work Integration</t>
+          <t>Study Work Integration</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -23134,7 +23094,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>work‑integrated learning; experiential education; career readiness; applied professional practice; study</t>
+          <t>work‑integrated learning; experiential education; career readiness; applied professional practice; study integration</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -23156,12 +23116,12 @@
       </c>
       <c r="T176" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U176" t="inlineStr">
         <is>
-          <t>keep:1, "Study-Work Integration":2</t>
+          <t>keep:0, "Study and Work Integration/Study Work Integration":3</t>
         </is>
       </c>
       <c r="V176" t="inlineStr">
@@ -23286,12 +23246,12 @@
         <v>0</v>
       </c>
       <c r="S177" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T177" t="inlineStr"/>
       <c r="U177" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "IT Competency Documentation":1</t>
         </is>
       </c>
       <c r="V177" t="inlineStr">
@@ -23525,7 +23485,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>scrum; kanban; sprint planning; backlog management; agile</t>
+          <t>scrum; kanban; sprint planning; backlog management; agile project management</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -23543,12 +23503,12 @@
         <v>0</v>
       </c>
       <c r="S179" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T179" t="inlineStr"/>
       <c r="U179" t="inlineStr">
         <is>
-          <t>keep:2, "Agile Methodology Application":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V179" t="inlineStr">
@@ -23695,9 +23655,13 @@
         <v>0</v>
       </c>
       <c r="Z180" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA180" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>Problem Solving</t>
+        </is>
+      </c>
       <c r="AB180" t="b">
         <v>0</v>
       </c>
@@ -24076,9 +24040,13 @@
         <v>0</v>
       </c>
       <c r="Z183" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA183" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>Problem Solving</t>
+        </is>
+      </c>
       <c r="AB183" t="b">
         <v>0</v>
       </c>
@@ -24129,7 +24097,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Productivity Monitoring</t>
+          <t>Project Progress Monitoring</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -24175,15 +24143,19 @@
         </is>
       </c>
       <c r="R184" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S184" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T184" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U184" t="inlineStr">
         <is>
-          <t>keep:2, "Project Progress Monitoring":1</t>
+          <t>keep:1, "Project Progress Monitoring":2</t>
         </is>
       </c>
       <c r="V184" t="inlineStr">
@@ -24514,7 +24486,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Requirement Analysis</t>
+          <t>Requirements Analysis</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -24545,7 +24517,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>business analysis; requirements elicitation; use case modeling; functional specification; requirement analysis</t>
+          <t>requirements elicitation; use case modeling; functional specification; requirement analysis; design solutions</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -24560,15 +24532,19 @@
         </is>
       </c>
       <c r="R187" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S187" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="T187" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U187" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "Requirements Analysis":2</t>
         </is>
       </c>
       <c r="V187" t="inlineStr">
@@ -24585,7 +24561,7 @@
         </is>
       </c>
       <c r="Y187" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z187" t="b">
         <v>1</v>
@@ -24821,12 +24797,12 @@
         <v>0</v>
       </c>
       <c r="S189" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T189" t="inlineStr"/>
       <c r="U189" t="inlineStr">
         <is>
-          <t>keep:2, "Solution Designing":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V189" t="inlineStr">
@@ -24930,7 +24906,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>reflection; sprint retrospective; project performance metrics; outcome analysis; continuous improvement</t>
+          <t>agile; sprint retrospective; project performance metrics; outcome analysis; continuous improvement</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -24957,7 +24933,7 @@
       </c>
       <c r="U190" t="inlineStr">
         <is>
-          <t>keep:1, "Sprint Project Outcome Reflection":2</t>
+          <t>keep:1, "Sprint Project Outcome Reflection/Outcome Reflection":2</t>
         </is>
       </c>
       <c r="V190" t="inlineStr">
@@ -24974,7 +24950,7 @@
         </is>
       </c>
       <c r="Y190" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z190" t="b">
         <v>0</v>
@@ -25084,7 +25060,7 @@
       <c r="T191" t="inlineStr"/>
       <c r="U191" t="inlineStr">
         <is>
-          <t>keep:2, "Stakeholder Needs Fulfilment":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V191" t="inlineStr">
@@ -25315,7 +25291,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>time; prioritisation; scheduling; task planning; process management</t>
+          <t>time; processes; prioritization; scheduling; task planning</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -25575,7 +25551,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>agile; project management; application; sprint planning; iterative development</t>
+          <t>agile; project management; scrum; sprint planning; iterative development</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -25615,7 +25591,7 @@
         </is>
       </c>
       <c r="Y195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z195" t="b">
         <v>0</v>
@@ -25673,7 +25649,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Problem Solving Application</t>
+          <t>Critical Thinking Application</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -25719,19 +25695,15 @@
         </is>
       </c>
       <c r="R196" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S196" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T196" t="inlineStr"/>
       <c r="U196" t="inlineStr">
         <is>
-          <t>keep:1, "Problem Solving Application":2</t>
+          <t>keep:2, "Problem Solving Application":1</t>
         </is>
       </c>
       <c r="V196" t="inlineStr">
@@ -25751,13 +25723,9 @@
         <v>1</v>
       </c>
       <c r="Z196" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA196" t="inlineStr">
-        <is>
-          <t>Problem Solving</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA196" t="inlineStr"/>
       <c r="AB196" t="b">
         <v>0</v>
       </c>
@@ -25970,7 +25938,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>design thinking; strategic planning; innovation management; design roadmap; development strategies</t>
+          <t>design thinking; strategic planning; design roadmap; development strategies; design strategies</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
@@ -25988,16 +25956,16 @@
         <v>1</v>
       </c>
       <c r="S198" t="n">
-        <v>0.9066666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U198" t="inlineStr">
         <is>
-          <t>keep:0, "Design Development Strategy Formulation/Strategy Formulation":3</t>
+          <t>keep:0, "Design Development Strategy Formulation":2, "Design-Development Strategy Formulation":1</t>
         </is>
       </c>
       <c r="V198" t="inlineStr">
@@ -26014,7 +25982,7 @@
         </is>
       </c>
       <c r="Y198" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z198" t="b">
         <v>0</v>
@@ -26275,9 +26243,13 @@
         <v>0</v>
       </c>
       <c r="Z200" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA200" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>Critical Thinking Application</t>
+        </is>
+      </c>
       <c r="AB200" t="b">
         <v>0</v>
       </c>
@@ -26361,7 +26333,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>digital literacy; professional ethics; technical communication; professional practice; IT service management (ITIL)</t>
+          <t>digital literacy; professional ethics; technical communication; professional practice; application</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -26388,7 +26360,7 @@
       </c>
       <c r="U201" t="inlineStr">
         <is>
-          <t>keep:0, "Professional Practice Application/IT Professional Practice Application":3</t>
+          <t>keep:0, "IT Professional Practice Application":3</t>
         </is>
       </c>
       <c r="V201" t="inlineStr">
@@ -26405,7 +26377,7 @@
         </is>
       </c>
       <c r="Y201" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z201" t="b">
         <v>1</v>
@@ -26600,7 +26572,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Project Deliverable Scheduling</t>
+          <t>Project Schedule Planning</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -26631,7 +26603,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>scheduling; Gantt chart; critical path method; project timeline; deliverable tracking</t>
+          <t>Gantt chart; critical path method; project timeline; deliverable tracking; schedule</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
@@ -26646,19 +26618,15 @@
         </is>
       </c>
       <c r="R203" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S203" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T203" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T203" t="inlineStr"/>
       <c r="U203" t="inlineStr">
         <is>
-          <t>keep:0, "Project Deliverable Scheduling":2, "Project Deliverable Management":1</t>
+          <t>keep:0, "Project Deliverable Scheduling":1, "Project Deliverable Management":1, "Project Deliverable Planning":1</t>
         </is>
       </c>
       <c r="V203" t="inlineStr">
@@ -26678,13 +26646,9 @@
         <v>1</v>
       </c>
       <c r="Z203" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA203" t="inlineStr">
-        <is>
-          <t>Stakeholder Needs Analysis (LLM verified, sim=0.71)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA203" t="inlineStr"/>
       <c r="AB203" t="b">
         <v>0</v>
       </c>
@@ -26786,7 +26750,7 @@
         <v>0</v>
       </c>
       <c r="S204" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="T204" t="inlineStr"/>
       <c r="U204" t="inlineStr">
@@ -26811,13 +26775,9 @@
         <v>0</v>
       </c>
       <c r="Z204" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA204" t="inlineStr">
-        <is>
-          <t>Time Management (LLM verified, sim=0.69)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA204" t="inlineStr"/>
       <c r="AB204" t="b">
         <v>0</v>
       </c>
@@ -26919,12 +26879,12 @@
         <v>0</v>
       </c>
       <c r="S205" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T205" t="inlineStr"/>
       <c r="U205" t="inlineStr">
         <is>
-          <t>keep:2, "Project Factors Communication":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V205" t="inlineStr">
@@ -27053,7 +27013,7 @@
       <c r="T206" t="inlineStr"/>
       <c r="U206" t="inlineStr">
         <is>
-          <t>keep:2, "Stakeholder Needs Prioritisation":1</t>
+          <t>keep:2, "Stakeholder and Project Analysis":1</t>
         </is>
       </c>
       <c r="V206" t="inlineStr">
@@ -27311,7 +27271,7 @@
       <c r="T208" t="inlineStr"/>
       <c r="U208" t="inlineStr">
         <is>
-          <t>keep:2, "Personal Time Management":1</t>
+          <t>keep:2, "Time and Process Management":1</t>
         </is>
       </c>
       <c r="V208" t="inlineStr">
@@ -27568,12 +27528,12 @@
         <v>0</v>
       </c>
       <c r="S210" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T210" t="inlineStr"/>
       <c r="U210" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Skill Transfer Demonstration":1</t>
         </is>
       </c>
       <c r="V210" t="inlineStr">
@@ -27802,7 +27762,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>defensive security; threat modeling; incident response; security operations; knowledge synthesis</t>
+          <t>defensive security; cybersecurity; threat modeling; incident response; security operations</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -27825,7 +27785,7 @@
       <c r="T212" t="inlineStr"/>
       <c r="U212" t="inlineStr">
         <is>
-          <t>keep:2, "Defensive Knowledge Synthesis":1</t>
+          <t>keep:2, "Defensive Security Knowledge Integration":1</t>
         </is>
       </c>
       <c r="V212" t="inlineStr">
@@ -27842,7 +27802,7 @@
         </is>
       </c>
       <c r="Y212" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z212" t="b">
         <v>0</v>
@@ -27928,7 +27888,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>ethics; legal regulations; compliance; ethical; constraints</t>
+          <t>ethics; legal regulations; compliance; constraints; code of conduct</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
@@ -27955,7 +27915,7 @@
       </c>
       <c r="U213" t="inlineStr">
         <is>
-          <t>keep:1, "Ethical Constraints Identification/Ethical Compliance Identification":2</t>
+          <t>keep:0, "Ethical Constraints Identification/Ethical Compliance Identification":2, "Ethical Legal Constraints Recognition":1</t>
         </is>
       </c>
       <c r="V213" t="inlineStr">
@@ -28076,12 +28036,12 @@
         <v>0</v>
       </c>
       <c r="S214" t="n">
-        <v>0.95</v>
+        <v>0.925</v>
       </c>
       <c r="T214" t="inlineStr"/>
       <c r="U214" t="inlineStr">
         <is>
-          <t>keep:2, "Ethical Hacking Technique Application":1</t>
+          <t>keep:2, "Security Vulnerability Exploitation":1</t>
         </is>
       </c>
       <c r="V214" t="inlineStr">
@@ -28184,7 +28144,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>penetration testing; vulnerability assessment; exploit development; cybersecurity tools; information security</t>
+          <t>penetration testing; vulnerability assessment; exploit development; cybersecurity tools; ethical hacking</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
@@ -28206,12 +28166,12 @@
       </c>
       <c r="T215" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U215" t="inlineStr">
         <is>
-          <t>keep:1, "Security Vulnerability Exploitation":2</t>
+          <t>keep:0, "Security Vulnerability Exploitation":3</t>
         </is>
       </c>
       <c r="V215" t="inlineStr">
@@ -28228,14 +28188,14 @@
         </is>
       </c>
       <c r="Y215" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z215" t="b">
         <v>1</v>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>Ethical Hacking Problem Solving (LLM verified, sim=0.66)</t>
+          <t>Penetration Testing Execution (LLM verified, sim=0.68)</t>
         </is>
       </c>
       <c r="AB215" t="b">
@@ -28444,7 +28404,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>ethical hacking; Metasploit; Kali Linux; penetration testing; execution</t>
+          <t>execution; ethical hacking; Metasploit; Kali Linux; penetration testing</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -28462,12 +28422,12 @@
         <v>0</v>
       </c>
       <c r="S217" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T217" t="inlineStr"/>
       <c r="U217" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Penetration Testing":1</t>
         </is>
       </c>
       <c r="V217" t="inlineStr">
@@ -28487,13 +28447,9 @@
         <v>1</v>
       </c>
       <c r="Z217" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA217" t="inlineStr">
-        <is>
-          <t>Ethical Hacking Problem Solving (LLM verified, sim=0.71)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA217" t="inlineStr"/>
       <c r="AB217" t="b">
         <v>0</v>
       </c>
@@ -28574,7 +28530,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>network security; countermeasure; explanation; threat mitigation; defense-in-depth</t>
+          <t>network security; countermeasure; encryption; threat mitigation; defense-in-depth</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
@@ -28614,7 +28570,7 @@
         </is>
       </c>
       <c r="Y218" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z218" t="b">
         <v>0</v>
@@ -28674,7 +28630,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Writes clear technical documents and speaks in presentations, translating complex concepts for academic audiences.</t>
+          <t>Writes clear technical documents and presentations, speaking to translate complex concepts for academic audiences.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -28747,9 +28703,13 @@
         <v>1</v>
       </c>
       <c r="Z219" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA219" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>Peer Communication</t>
+        </is>
+      </c>
       <c r="AB219" t="b">
         <v>0</v>
       </c>
@@ -28933,7 +28893,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Data Analytics Modelling</t>
+          <t>Data Analytics Application</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -28964,7 +28924,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>supervised learning; unsupervised learning; clustering algorithms; classification modelling; analytics</t>
+          <t>supervised learning; unsupervised learning; regression analysis; clustering algorithms; classification modelling</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
@@ -28986,12 +28946,12 @@
       </c>
       <c r="T221" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U221" t="inlineStr">
         <is>
-          <t>keep:0, "Data Analytics Modelling":2, "Data Analytics Application":1</t>
+          <t>keep:0, "Data Analytics Application":3</t>
         </is>
       </c>
       <c r="V221" t="inlineStr">
@@ -29008,7 +28968,7 @@
         </is>
       </c>
       <c r="Y221" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z221" t="b">
         <v>1</v>
@@ -29121,7 +29081,7 @@
       <c r="T222" t="inlineStr"/>
       <c r="U222" t="inlineStr">
         <is>
-          <t>keep:2, "Clustering Application":1</t>
+          <t>keep:1, "Clustering Technique Application":1, "Data Analytics Application":1</t>
         </is>
       </c>
       <c r="V222" t="inlineStr">
@@ -29141,13 +29101,9 @@
         <v>0</v>
       </c>
       <c r="Z222" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA222" t="inlineStr">
-        <is>
-          <t>Regression Modelling</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA222" t="inlineStr"/>
       <c r="AB222" t="b">
         <v>0</v>
       </c>
@@ -29228,7 +29184,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>data analytics application; data analytics; quantitative analysis; data visualization; data analytics principles</t>
+          <t>data analytics; evidence-based evaluation; quantitative analysis; data visualization; data analytics principles</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
@@ -29272,12 +29228,16 @@
         </is>
       </c>
       <c r="Y223" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z223" t="b">
         <v>1</v>
       </c>
-      <c r="Z223" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA223" t="inlineStr"/>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>Evidence Evaluation (LLM verified, sim=0.73)</t>
+        </is>
+      </c>
       <c r="AB223" t="b">
         <v>0</v>
       </c>
@@ -29376,12 +29336,12 @@
         <v>0</v>
       </c>
       <c r="S224" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T224" t="inlineStr"/>
       <c r="U224" t="inlineStr">
         <is>
-          <t>keep:2, "Cyber Security Data Processing":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V224" t="inlineStr">
@@ -29457,7 +29417,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Cyber Security Data Processing</t>
+          <t>Cyber Security Data Analysis</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -29488,7 +29448,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>threat intelligence; SIEM; log analysis; network traffic analytics; processing</t>
+          <t>threat intelligence; SIEM; log analysis; network traffic analytics; cyber security data</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
@@ -29503,15 +29463,19 @@
         </is>
       </c>
       <c r="R225" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S225" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="T225" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="U225" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Cyber Security Data Analysis":3</t>
         </is>
       </c>
       <c r="V225" t="inlineStr">
@@ -29528,7 +29492,7 @@
         </is>
       </c>
       <c r="Y225" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z225" t="b">
         <v>1</v>
@@ -29636,12 +29600,12 @@
         <v>0</v>
       </c>
       <c r="S226" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T226" t="inlineStr"/>
       <c r="U226" t="inlineStr">
         <is>
-          <t>keep:2, "Cyber Security Data Processing":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V226" t="inlineStr">
@@ -30018,12 +29982,12 @@
         <v>0</v>
       </c>
       <c r="S229" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T229" t="inlineStr"/>
       <c r="U229" t="inlineStr">
         <is>
-          <t>keep:2, "Evidence Provision Evaluation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V229" t="inlineStr">
@@ -30278,12 +30242,12 @@
         <v>0</v>
       </c>
       <c r="S231" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T231" t="inlineStr"/>
       <c r="U231" t="inlineStr">
         <is>
-          <t>keep:2, "Data Analytics Solution Implementation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V231" t="inlineStr">
@@ -30355,7 +30319,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Regression Modelling</t>
+          <t>Data Analytics Application</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -30386,7 +30350,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>supervised learning; predictive analytics; statistical modeling; machine learning; regression</t>
+          <t>supervised learning; statistical modeling; machine learning; regression; unsupervised learning</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
@@ -30401,15 +30365,19 @@
         </is>
       </c>
       <c r="R232" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S232" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T232" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U232" t="inlineStr">
         <is>
-          <t>keep:1, "Regression Supervised Learning":1, "Data Analytics Application":1</t>
+          <t>keep:1, "Data Analytics Application":2</t>
         </is>
       </c>
       <c r="V232" t="inlineStr">
@@ -30426,12 +30394,16 @@
         </is>
       </c>
       <c r="Y232" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z232" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA232" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>Clustering Analysis</t>
+        </is>
+      </c>
       <c r="AB232" t="b">
         <v>0</v>
       </c>
@@ -30512,7 +30484,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>cybersecurity analytics; data analysis techniques; statistical modeling; analytical methodology; learning</t>
+          <t>cybersecurity analytics; data analysis techniques; research methods; statistical modeling; analytical methodology</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
@@ -30530,12 +30502,12 @@
         <v>0</v>
       </c>
       <c r="S233" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T233" t="inlineStr"/>
       <c r="U233" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Data Analytics Methodology Learning":1</t>
         </is>
       </c>
       <c r="V233" t="inlineStr">
@@ -30552,7 +30524,7 @@
         </is>
       </c>
       <c r="Y233" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z233" t="b">
         <v>0</v>
@@ -30656,12 +30628,12 @@
         <v>0</v>
       </c>
       <c r="S234" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T234" t="inlineStr"/>
       <c r="U234" t="inlineStr">
         <is>
-          <t>keep:2, "Evidence Provision Evaluation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V234" t="inlineStr">
@@ -30785,7 +30757,7 @@
       <c r="T235" t="inlineStr"/>
       <c r="U235" t="inlineStr">
         <is>
-          <t>keep:1, "Introductory Unit Completion":1, "Online Unit Passing":1</t>
+          <t>keep:2, "Introductory Unit Completion":1</t>
         </is>
       </c>
       <c r="V235" t="inlineStr">
@@ -30909,7 +30881,7 @@
       <c r="T236" t="inlineStr"/>
       <c r="U236" t="inlineStr">
         <is>
-          <t>keep:1, "Career Education Demonstration":1, "Career Education Journey Development":1</t>
+          <t>keep:1, "Career Education Journey Development":1, "Career Education Demonstration":1</t>
         </is>
       </c>
       <c r="V236" t="inlineStr">
@@ -31382,7 +31354,7 @@
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>e‑learning; learning management system; completion; self‑paced online instruction; introductory unit</t>
+          <t>e‑learning; learning management system; completion; self‑paced online instruction; unit</t>
         </is>
       </c>
       <c r="O240" t="inlineStr">
@@ -31404,12 +31376,12 @@
       </c>
       <c r="T240" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>keep:1, "Online Unit Completion":2</t>
+          <t>keep:0, "Online Unit Completion":3</t>
         </is>
       </c>
       <c r="V240" t="inlineStr">
@@ -31514,7 +31486,7 @@
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>career development; professional identity; self‑reflection; education; career counseling</t>
+          <t>career development; professional identity; self‑reflection; personal branding; education</t>
         </is>
       </c>
       <c r="O241" t="inlineStr">
@@ -31536,12 +31508,12 @@
       </c>
       <c r="T241" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U241" t="inlineStr">
         <is>
-          <t>keep:1, "Career Education Development/Career Education Journey Development":2</t>
+          <t>keep:0, "Career Education Development":3</t>
         </is>
       </c>
       <c r="V241" t="inlineStr">

--- a/skills_refined.xlsx
+++ b/skills_refined.xlsx
@@ -763,7 +763,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>academic integrity; honesty; ethical conduct; honor code; behaviours</t>
+          <t>academic integrity; honesty; ethical conduct; honor code; acceptable and unacceptable behaviours</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>keep:0, "Academic Integrity Identification":3</t>
+          <t>keep:1, "Academic Integrity Identification":2</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>academic integrity; honour code; misconduct detection; behaviour; acceptable behaviours</t>
+          <t>academic integrity; ethical standards; honor code; behaviour; acceptable behaviours</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1045,12 +1045,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>keep:0, "Academic Integrity Behaviour Identification":3</t>
+          <t>keep:1, "Academic Integrity Behaviour Identification":2</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Academic Integrity Application</t>
+          <t>Academic Integrity Strategy Application</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>academic integrity; research ethics; compliance; moral reasoning; decision making</t>
+          <t>academic integrity; strategies; compliance; decision making; research ethics</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>keep:0, "Academic Integrity Application":3</t>
+          <t>keep:0, "Academic Integrity Application/Academic Integrity Strategy Application":3</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="Y5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="b">
         <v>1</v>
@@ -1305,12 +1305,12 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Academic Integrity Values Application":1</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1330,13 +1330,9 @@
         <v>0</v>
       </c>
       <c r="Z6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Responsibility Application</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="b">
         <v>0</v>
       </c>
@@ -1460,13 +1456,9 @@
         <v>0</v>
       </c>
       <c r="Z7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Harm Support Identification</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="b">
         <v>0</v>
       </c>
@@ -1799,7 +1791,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>healthy relationships; respectful relationships; characteristics; boundaries; consent</t>
+          <t>healthy relationships; respectful relationships; relationship characteristics; boundaries; consent</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1902,7 +1894,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Responsibility Application</t>
+          <t>Academic Integrity Responsibility Application</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1933,7 +1925,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>academic integrity; ethics; accountability; responsibility; application</t>
+          <t>academic integrity; ethics; accountability; responsibility; honesty</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1948,15 +1940,19 @@
         </is>
       </c>
       <c r="R11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T11" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>keep:2, "Academic Integrity Values Application":1</t>
+          <t>keep:1, "Academic Integrity Responsibility Application/Academic Integrity Values Application":2</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1973,16 +1969,12 @@
         </is>
       </c>
       <c r="Y11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Trust Application</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="b">
         <v>0</v>
       </c>
@@ -2063,7 +2055,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>healthy relationships; respectful interaction; boundaries and consent; interpersonal dynamics; safe respectful relationships</t>
+          <t>healthy relationships; respectful interaction; boundaries and consent; characteristics; safe relationships</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2081,12 +2073,12 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Respectful Relationship Characteristics Identification":1</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -2158,7 +2150,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Harm Support Identification</t>
+          <t>Support Seeking Identification</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2189,7 +2181,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>mental health; risk assessment; crisis intervention; self‑harm screening; harm</t>
+          <t>mental health; risk assessment; crisis intervention; self‑harm screening; support seeking</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2204,15 +2196,19 @@
         </is>
       </c>
       <c r="R13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T13" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>keep:2, "Support Resource Identification":1</t>
+          <t>keep:1, "Support Seeking Identification":2</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -2229,12 +2225,16 @@
         </is>
       </c>
       <c r="Y13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Harm Support Referral Identification</t>
+        </is>
+      </c>
       <c r="AB13" t="b">
         <v>0</v>
       </c>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>keep:1, "Support Resource Identification/Support Seeking Identification":2</t>
+          <t>keep:1, "Support Resource Identification":2</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -2467,12 +2467,12 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>keep:2, "Academic Integrity Trust Application":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2492,9 +2492,13 @@
         <v>0</v>
       </c>
       <c r="Z15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Fairness Application</t>
+        </is>
+      </c>
       <c r="AB15" t="b">
         <v>0</v>
       </c>
@@ -3300,7 +3304,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Portfolio Artefact Evaluation</t>
+          <t>Portfolio Quality Analysis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3331,7 +3335,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>portfolio assessment; artefact evaluation; reflective analysis; e‑portfolio review; critique</t>
+          <t>portfolio assessment; artefact evaluation; reflective analysis; quality; e‑portfolio review</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -3346,19 +3350,15 @@
         </is>
       </c>
       <c r="R22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>keep:1, "Portfolio Artefact Evaluation/Portfolio Quality Evaluation":2</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="b">
         <v>0</v>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Procedural Code Evaluation</t>
+          <t>Procedural Program Code Evaluation</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>code review; coding standards; static analysis; software quality assurance; procedural code</t>
+          <t>code review; coding standards; static analysis; procedural code; program code</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -3476,15 +3476,19 @@
         </is>
       </c>
       <c r="R23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T23" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>keep:2, "Procedural Code Convention Evaluation":1</t>
+          <t>keep:1, "Procedural Program Code Evaluation/Procedural Code Convention Evaluation":2</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -3501,7 +3505,7 @@
         </is>
       </c>
       <c r="Y23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="b">
         <v>0</v>
@@ -3740,7 +3744,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>keep:0, "Program Structure Explanation/Program Explanation":3</t>
+          <t>keep:0, "Program Function Explanation/Program Explanation":3</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3843,7 +3847,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>software; cybersecurity; vulnerability assessment; risk management; security best practices</t>
+          <t>software; cybersecurity; vulnerability assessment; security best practices; familiarisation</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -3861,12 +3865,12 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Security Familiarisation":1</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3883,7 +3887,7 @@
         </is>
       </c>
       <c r="Y26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z26" t="b">
         <v>0</v>
@@ -3969,7 +3973,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>fundamentals; learning; structured programming; control structures; procedural programming</t>
+          <t>procedural programming; control structures; algorithmic thinking; structured programming; fundamentals</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -4099,7 +4103,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>procedural programming; data types; control flow; modularisation; programming languages</t>
+          <t>procedural programming; data types; control flow; modularisation; application development</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -4143,7 +4147,7 @@
         </is>
       </c>
       <c r="Y28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="b">
         <v>1</v>
@@ -4256,12 +4260,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>keep:0, "Competency Reflection":3</t>
+          <t>keep:1, "Competency Reflection":2</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -4365,7 +4369,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>system architecture; hardware integration; OS configuration; computing systems; building computing systems</t>
+          <t>system architecture; hardware integration; OS configuration; computing systems; system construction</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -4383,12 +4387,12 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
-          <t>keep:2, "Computing System Development":1</t>
+          <t>keep:0, "Computing System Development":1, "Computer System Configuration":1, "Computer System Construction":1</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -4408,9 +4412,13 @@
         <v>1</v>
       </c>
       <c r="Z30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Computer System Configuration (LLM verified, sim=0.66)</t>
+        </is>
+      </c>
       <c r="AB30" t="b">
         <v>0</v>
       </c>
@@ -4461,7 +4469,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Embedded System Prototyping</t>
+          <t>Microcontroller System Prototyping</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4492,7 +4500,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>microcontroller; firmware development; embedded system; Arduino; prototyping</t>
+          <t>microcontroller; firmware development; PCB design; prototyping; digital systems</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -4507,15 +4515,19 @@
         </is>
       </c>
       <c r="R31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="T31" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "Microcontroller System Prototyping":2</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -4619,7 +4631,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>computer architecture; hardware-software interface; system components; operating system fundamentals; foundations</t>
+          <t>computer architecture; system components; description; elements; foundations</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -4663,7 +4675,7 @@
         </is>
       </c>
       <c r="Y32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z32" t="b">
         <v>1</v>
@@ -4723,7 +4735,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>IT Professional Competency Identification</t>
+          <t>IT Professional Characteristics Identification</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4754,7 +4766,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>IT competency frameworks; professional standards; ethical guidelines; role expectations; characteristics</t>
+          <t>IT competency frameworks; professional standards; role expectations; characteristics; information technology professionals</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -4769,15 +4781,19 @@
         </is>
       </c>
       <c r="R33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T33" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>keep:2, "IT Professional Characteristics Identification":1</t>
+          <t>keep:0, "IT Professional Characteristics Identification":3</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -4794,7 +4810,7 @@
         </is>
       </c>
       <c r="Y33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z33" t="b">
         <v>0</v>
@@ -5008,7 +5024,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>information literacy; digital libraries; e‑learning platforms; learning resources; resource utilisation</t>
+          <t>information literacy; research skills; e‑learning platforms; learning resources; resource utilisation</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -5031,7 +5047,7 @@
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
-          <t>keep:2, "Learning Resource Acquisition":1</t>
+          <t>keep:1, "Learning Resource Acquisition":1, "Learning Resource Seeking Utilisation":1</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -5412,7 +5428,7 @@
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
-          <t>keep:2, "Unix System Configuration":1</t>
+          <t>keep:2, "Computer System Configuration-Operation":1</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -5432,13 +5448,9 @@
         <v>0</v>
       </c>
       <c r="Z38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>Unix System Configuration</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="b">
         <v>0</v>
       </c>
@@ -5494,7 +5506,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Engages with computer system evolution in the context of emerging technology trends.</t>
+          <t>Engages with computer system evolution on emerging technology trends.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5616,7 +5628,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Unix System Configuration</t>
+          <t>Computer System Configuration</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5647,7 +5659,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Unix; Linux; system administration; shell scripting; configuration management</t>
+          <t>Unix; system administration; shell scripting; configuration management; computer</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -5662,15 +5674,19 @@
         </is>
       </c>
       <c r="R40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S40" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T40" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>keep:2, "Computer System Configuration":1</t>
+          <t>keep:0, "Computer System Configuration":3</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -5687,12 +5703,16 @@
         </is>
       </c>
       <c r="Y40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>Computer System Configuration</t>
+        </is>
+      </c>
       <c r="AB40" t="b">
         <v>0</v>
       </c>
@@ -5816,9 +5836,13 @@
         <v>0</v>
       </c>
       <c r="Z41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Security Controls Implementation (LLM verified, sim=0.73)</t>
+        </is>
+      </c>
       <c r="AB41" t="b">
         <v>0</v>
       </c>
@@ -5868,7 +5892,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Attack Impact Assessment</t>
+          <t>Attack Impact Effectiveness Assessment</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5899,7 +5923,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>attack; threat modeling; vulnerability assessment; security controls effectiveness; impact analysis</t>
+          <t>attack; vulnerability assessment; security controls effectiveness; impact analysis; countermeasures</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -5914,15 +5938,19 @@
         </is>
       </c>
       <c r="R42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T42" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>keep:2, "Attack Countermeasure Effectiveness Assessment":1</t>
+          <t>keep:0, "Attack Impact Effectiveness Assessment/Attack Impact Countermeasure Assessment":2, "Attack Impact-Countermeasure Assessment":1</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -5939,7 +5967,7 @@
         </is>
       </c>
       <c r="Y42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z42" t="b">
         <v>0</v>
@@ -6043,7 +6071,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr">
@@ -6068,9 +6096,13 @@
         <v>0</v>
       </c>
       <c r="Z43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Cyber Attack Handling (LLM verified, sim=0.78)</t>
+        </is>
+      </c>
       <c r="AB43" t="b">
         <v>0</v>
       </c>
@@ -6151,7 +6183,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>encryption algorithms; public key infrastructure; TLS/SSL protocols; cryptographic key management; cryptography application</t>
+          <t>encryption algorithms; public key infrastructure; TLS/SSL protocols; network security; cryptographic key management</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -6169,12 +6201,12 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
-          <t>keep:2, "Cryptography Approach Explanation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -6191,7 +6223,7 @@
         </is>
       </c>
       <c r="Y44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="b">
         <v>0</v>
@@ -6295,12 +6327,12 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.95</v>
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Cyber Attack Detection Mitigation":1</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -6320,13 +6352,9 @@
         <v>0</v>
       </c>
       <c r="Z45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>Case Study Analysis (LLM verified, sim=0.78)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA45" t="inlineStr"/>
       <c r="AB45" t="b">
         <v>0</v>
       </c>
@@ -6376,7 +6404,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cyber Security Fundamentals Learning</t>
+          <t>Cyber Security Practices Learning</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6407,7 +6435,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>information security; threat modeling; risk assessment; cyber security fundamentals; real world practices</t>
+          <t>threat modeling; risk assessment; security frameworks; practices; learning</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -6422,15 +6450,19 @@
         </is>
       </c>
       <c r="R46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T46" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>keep:2, "Cyber Security Practices Learning":1</t>
+          <t>keep:1, "Cyber Security Practices Learning":2</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -6450,17 +6482,17 @@
         <v>1</v>
       </c>
       <c r="Z46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA46" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Cyber Security Problem Solving (LLM verified, sim=0.72)</t>
+        </is>
+      </c>
       <c r="AB46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>vague skill from course description — "Cyber Security Fundamentals Learning" uses non-assessable term: {'fundamentals'}</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC46" t="inlineStr"/>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6580,13 +6612,9 @@
         <v>0</v>
       </c>
       <c r="Z47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>Cyber Security Fundamentals Learning (LLM verified, sim=0.72)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="b">
         <v>0</v>
       </c>
@@ -6690,7 +6718,7 @@
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr">
         <is>
-          <t>keep:2, "Network Risk Concept Exploration":1</t>
+          <t>keep:2, "Communication Network Risks Exploration":1</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -7067,12 +7095,12 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Cyber Security Tool Implementation":1</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -7202,7 +7230,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>keep:0, "Threat Vulnerability Understanding":2, "Threat Vulnerability Assessment":1</t>
+          <t>keep:1, "Threat Vulnerability Understanding":2</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -7404,7 +7432,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Discrete Mathematics Tools Application</t>
+          <t>Discrete Mathematics Application</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -7435,7 +7463,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>discrete mathematics; complexity analysis; algorithm design; computational theory; mathematical tools</t>
+          <t>discrete mathematics; complexity analysis; application; algorithm design; computational theory</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -7450,19 +7478,15 @@
         </is>
       </c>
       <c r="R54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr">
         <is>
-          <t>keep:0, "Discrete Mathematics Tool Application/Discrete Mathematics Tools Application":3</t>
+          <t>keep:2, "Discrete Mathematics Tools Application":1</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -7479,7 +7503,7 @@
         </is>
       </c>
       <c r="Y54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="b">
         <v>0</v>
@@ -7709,12 +7733,12 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr">
         <is>
-          <t>keep:2, "Discrete Mathematics Foundations Exploration":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -7817,7 +7841,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>network analysis; graph algorithms; combinatorial optimisation; graph theory; graph theory application</t>
+          <t>network analysis; graph algorithms; combinatorial optimisation; discrete mathematics; graph theory</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -7857,12 +7881,16 @@
         </is>
       </c>
       <c r="Y57" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z57" t="b">
         <v>1</v>
       </c>
-      <c r="Z57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>Number Theory Application</t>
+        </is>
+      </c>
       <c r="AB57" t="b">
         <v>0</v>
       </c>
@@ -8038,7 +8066,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Number Theory Exploration</t>
+          <t>Number Theory Application</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -8069,7 +8097,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>analytic number theory; prime distribution; modular arithmetic; Diophantine equations; mathematical proofs</t>
+          <t>analytic number theory; modular arithmetic; Diophantine equations; mathematical proofs; application</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -8084,41 +8112,41 @@
         </is>
       </c>
       <c r="R59" t="b">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>keep:2, "Number Theory Exploration":1</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Covers number theory concepts to solve hybrid coursework problems.</t>
+        </is>
+      </c>
+      <c r="W59" t="b">
+        <v>0</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>analytic number theory, prime distribution, modular arithmetic, Diophantine equations, mathematical proofs</t>
+        </is>
+      </c>
+      <c r="Y59" t="b">
         <v>1</v>
       </c>
-      <c r="S59" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>keep:0, "Number Theory Exploration":3</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Covers number theory concepts to solve hybrid coursework problems.</t>
-        </is>
-      </c>
-      <c r="W59" t="b">
-        <v>0</v>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>analytic number theory, prime distribution, modular arithmetic, Diophantine equations, mathematical proofs</t>
-        </is>
-      </c>
-      <c r="Y59" t="b">
-        <v>0</v>
-      </c>
       <c r="Z59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA59" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>Set Theory Application</t>
+        </is>
+      </c>
       <c r="AB59" t="b">
         <v>0</v>
       </c>
@@ -8168,7 +8196,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Predicate Logic Reasoning</t>
+          <t>Predicate Logic Application</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -8199,7 +8227,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>first-order logic; formal proof; logical inference; predicate; reasoning</t>
+          <t>first-order logic; formal proof; logical inference; predicate; application</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -8214,15 +8242,19 @@
         </is>
       </c>
       <c r="R60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S60" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="T60" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>keep:2, "Predicate Logic Application":1</t>
+          <t>keep:1, "Predicate Logic Application":2</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -8239,12 +8271,16 @@
         </is>
       </c>
       <c r="Y60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA60" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>Propositional Logic Application</t>
+        </is>
+      </c>
       <c r="AB60" t="b">
         <v>0</v>
       </c>
@@ -8325,7 +8361,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>formal logic; logical inference; truth tables; propositional logic; application</t>
+          <t>formal logic; logical inference; truth tables; propositional logic; logic application</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -8347,12 +8383,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>keep:1, "Propositional Logic Application":2</t>
+          <t>keep:0, "Propositional Logic Application":3</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -8424,7 +8460,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Recurrence Understanding</t>
+          <t>Recurrence Analysis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -8470,19 +8506,15 @@
         </is>
       </c>
       <c r="R62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr">
         <is>
-          <t>keep:0, "Recurrence Understanding":2, "Recurrence Application":1</t>
+          <t>keep:0, "Recurrence Application":1, "Recurrence Examination":1, "Recurrence Exploration":1</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -8603,12 +8635,12 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "Set Theory Exploration":1, "Set Theory Understanding":1</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -8628,13 +8660,9 @@
         <v>0</v>
       </c>
       <c r="Z63" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>Graph Theory Application</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA63" t="inlineStr"/>
       <c r="AB63" t="b">
         <v>0</v>
       </c>
@@ -8810,7 +8838,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Problem Solving Strategy Development</t>
+          <t>Problem Solving Strategy Design</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -8841,7 +8869,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>rigorous strategies; first‑principles reasoning; problem-solving strategies; mathematical problem solving; discrete mathematics</t>
+          <t>rigorous strategies; first‑principles reasoning; problem-solving strategies; mathematical problem solving; design</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -8868,7 +8896,7 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>keep:0, "Problem Solving Strategy Development":2, "Problem-Solving Strategy Development":1</t>
+          <t>keep:0, "Problem Solving Strategy Design":2, "Problem Solving Strategy Development":1</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -8885,7 +8913,7 @@
         </is>
       </c>
       <c r="Y65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z65" t="b">
         <v>0</v>
@@ -8989,12 +9017,12 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr">
         <is>
-          <t>keep:1, "Network Architecture Assessment":1, "Network Construction Review":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -9097,7 +9125,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>networking; data flow; TCP/IP; OSI model; explanation</t>
+          <t>networking; data transmission; data flow; TCP/IP; OSI model</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -9119,12 +9147,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>keep:1, "Network Data Flow Explanation/Data Flow Explanation":2</t>
+          <t>keep:0, "Network Data Flow Explanation":3</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -9141,7 +9169,7 @@
         </is>
       </c>
       <c r="Y67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="b">
         <v>0</v>
@@ -9196,7 +9224,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Network Program Development</t>
+          <t>Network Programming Development</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -9242,19 +9270,15 @@
         </is>
       </c>
       <c r="R68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr">
         <is>
-          <t>keep:0, "Network Program Development":3</t>
+          <t>keep:2, "Network Program Development":1</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -9326,7 +9350,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Network Protocol Explanation</t>
+          <t>Network Protocol Understanding</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -9357,7 +9381,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>OSI model; TCP/IP stack; packet switching; routing protocols; Wireshark analysis</t>
+          <t>OSI model; TCP/IP stack; packet switching; routing protocols; understanding</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -9372,45 +9396,45 @@
         </is>
       </c>
       <c r="R69" t="b">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>keep:1, "Network Protocol Comprehension":1, "Network Protocol Stack Explanation":1</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Network protocol fundamentals related to cyber security risks and secure architectures.</t>
+        </is>
+      </c>
+      <c r="W69" t="b">
+        <v>0</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>OSI model, TCP/IP stack, packet switching, routing protocols, Wireshark analysis</t>
+        </is>
+      </c>
+      <c r="Y69" t="b">
         <v>1</v>
-      </c>
-      <c r="S69" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>keep:1, "Network Protocol Explanation":2</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Network protocol fundamentals related to cyber security risks and secure architectures.</t>
-        </is>
-      </c>
-      <c r="W69" t="b">
-        <v>0</v>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>OSI model, TCP/IP stack, packet switching, routing protocols, Wireshark analysis</t>
-        </is>
-      </c>
-      <c r="Y69" t="b">
-        <v>0</v>
       </c>
       <c r="Z69" t="b">
         <v>0</v>
       </c>
       <c r="AA69" t="inlineStr"/>
       <c r="AB69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC69" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>vague skill from course description — "Network Protocol Understanding" uses non-assessable term: {'understanding'}</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -9487,7 +9511,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>OSI model; TCP/IP layers; network abstraction; network protocol stack; explanation</t>
+          <t>OSI model; TCP/IP layers; protocol encapsulation; network abstraction; network protocol stack</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -9527,7 +9551,7 @@
         </is>
       </c>
       <c r="Y70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="b">
         <v>0</v>
@@ -9582,7 +9606,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Network Scalability Assessment</t>
+          <t>Network Scalability Analysis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -9628,15 +9652,19 @@
         </is>
       </c>
       <c r="R71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S71" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T71" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>keep:2, "Network Scalability Analysis":1</t>
+          <t>keep:1, "Network Scalability Analysis":2</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -9656,9 +9684,13 @@
         <v>1</v>
       </c>
       <c r="Z71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA71" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>Network Issue Analysis</t>
+        </is>
+      </c>
       <c r="AB71" t="b">
         <v>0</v>
       </c>
@@ -9782,13 +9814,9 @@
         <v>0</v>
       </c>
       <c r="Z72" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>Network Data Analysis (LLM verified, sim=0.62)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="b">
         <v>0</v>
       </c>
@@ -9838,7 +9866,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Network Solution Design</t>
+          <t>Network Solution Provision</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -9869,7 +9897,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>network architecture; routing protocols; LAN/WAN design; software-defined networking; network solution</t>
+          <t>network architecture; routing protocols; LAN/WAN design; networking solutions; network solution</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -9884,15 +9912,19 @@
         </is>
       </c>
       <c r="R73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S73" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T73" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>keep:2, "Network Solution Development":1</t>
+          <t>keep:1, "Network Solution Provision/Networking Solution Provision":2</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -9909,7 +9941,7 @@
         </is>
       </c>
       <c r="Y73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z73" t="b">
         <v>0</v>
@@ -10013,12 +10045,12 @@
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Network Configuration Analysis":1</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -10139,12 +10171,12 @@
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr">
         <is>
-          <t>keep:2, "Protocol Implementation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -10274,7 +10306,7 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>keep:0, "Network Construction Review":1, "Network Construction Assessment":1, "Network Construction Evaluation":1</t>
+          <t>keep:0, "Network Construction Analysis":1, "Network Construction Review":1, "Network Construction Evaluation":1</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -10399,12 +10431,12 @@
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr">
         <is>
-          <t>keep:2, "Cloud API Security Configuration":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -10424,9 +10456,13 @@
         <v>0</v>
       </c>
       <c r="Z77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA77" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>Secure Database Design</t>
+        </is>
+      </c>
       <c r="AB77" t="b">
         <v>0</v>
       </c>
@@ -10476,7 +10512,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Program Code Analysis</t>
+          <t>Program Code Design Analysis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -10507,7 +10543,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>static code analysis; software security; secure coding practices; OWASP guidelines; program code</t>
+          <t>static code analysis; software security; secure coding practices; design; program code</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -10522,15 +10558,19 @@
         </is>
       </c>
       <c r="R78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
-      </c>
-      <c r="T78" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>keep:0, "Code Design Analysis":1, "Program Code-Documentation Analysis":1, "Programming Problems Identification":1</t>
+          <t>keep:0, "Program Code Design Analysis/Program Code Documentation Analysis":2, "Code Documentation Analysis":1</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -10547,7 +10587,7 @@
         </is>
       </c>
       <c r="Y78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z78" t="b">
         <v>0</v>
@@ -10633,7 +10673,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>software security tools; data validation; validation frameworks; automated testing; data integrity checks</t>
+          <t>software security tools; data integrity checks; validation frameworks; automated testing; data validation</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -10655,12 +10695,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>keep:1, "Data Validation Implementation":2</t>
+          <t>keep:0, "Data Validation Implementation":3</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -10781,12 +10821,12 @@
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Software Dynamic Analysis Testing":1</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -10806,13 +10846,9 @@
         <v>0</v>
       </c>
       <c r="Z80" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>Static Analysis Testing</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA80" t="inlineStr"/>
       <c r="AB80" t="b">
         <v>0</v>
       </c>
@@ -10988,7 +11024,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Programming Issue Mitigation</t>
+          <t>Program Issue Mitigation</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -11019,7 +11055,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>risk assessment; mitigation strategies; issue reporting; static analysis; programming</t>
+          <t>risk assessment; mitigation strategies; issue reporting; programming; program</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -11041,12 +11077,12 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>keep:0, "Programming Issue Mitigation":3</t>
+          <t>keep:1, "Program Issue Mitigation/Programming Issue Mitigation":2</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -11063,7 +11099,7 @@
         </is>
       </c>
       <c r="Y82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z82" t="b">
         <v>0</v>
@@ -11297,12 +11333,12 @@
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Secure Continuous Delivery Modelling":1</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -11374,7 +11410,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Database Security Planning</t>
+          <t>Secure Database Design</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -11405,7 +11441,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>encryption; access control; database; design; cloud API security</t>
+          <t>encryption; access control; database; secure; design</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -11420,19 +11456,15 @@
         </is>
       </c>
       <c r="R85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr">
         <is>
-          <t>keep:0, "Database Security Planning":2, "Secure Database Designing":1</t>
+          <t>keep:2, "Secure Database Designing":1</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -11449,16 +11481,12 @@
         </is>
       </c>
       <c r="Y85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>Cloud API Security Implementation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA85" t="inlineStr"/>
       <c r="AB85" t="b">
         <v>0</v>
       </c>
@@ -11557,12 +11585,12 @@
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr">
         <is>
-          <t>keep:0, "Secure Coding Application":1, "Secure Software Design Application":1, "Software Design Security Implementation":1</t>
+          <t>keep:1, "Software Design Security Implementation":1, "Software Design Securing":1</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -11665,7 +11693,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>secure coding; threat modelling; vulnerability assessment; principle; explanation</t>
+          <t>secure coding; threat modeling; vulnerability assessment; principle; explanation</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -11834,9 +11862,13 @@
         <v>0</v>
       </c>
       <c r="Z88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA88" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>Dynamic Analysis Testing</t>
+        </is>
+      </c>
       <c r="AB88" t="b">
         <v>0</v>
       </c>
@@ -11886,7 +11918,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Secure Coding Principles Explanation</t>
+          <t>Secure Coding Explanation</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -11917,7 +11949,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>secure coding principles; technical writing; audience tailoring; cybersecurity communication; code review facilitation</t>
+          <t>secure coding principles; technical writing; audience tailoring; cybersecurity communication; secure coding explanation</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -11939,12 +11971,12 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>keep:0, "Secure Coding Principles Explanation/Secure Coding Explanation/Secure Coding Principle Explanation":3</t>
+          <t>keep:1, "Secure Coding Explanation":2</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -11961,7 +11993,7 @@
         </is>
       </c>
       <c r="Y89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z89" t="b">
         <v>1</v>
@@ -12433,7 +12465,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>mediation; negotiation; dispute resolution; emotional intelligence; conflict</t>
+          <t>conflict management; mediation; negotiation; dispute resolution; emotional intelligence</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -12451,12 +12483,12 @@
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Conflict Management Observation":1</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
@@ -12582,7 +12614,7 @@
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr">
         <is>
-          <t>keep:2, "Skill Development":1</t>
+          <t>keep:2, "Professional Development Engagement":1</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -12654,7 +12686,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cybersecurity Risk Assessment</t>
+          <t>Cybersecurity Evaluation</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -12685,7 +12717,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>threat modeling; vulnerability assessment; risk management; NIST framework; cybersecurity</t>
+          <t>threat modeling; vulnerability assessment; risk management; cybersecurity; regulatory requirements</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -12700,15 +12732,19 @@
         </is>
       </c>
       <c r="R95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S95" t="n">
-        <v>0</v>
-      </c>
-      <c r="T95" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>keep:0, "Cybersecurity Assessment":1, "Cybersecurity Evaluation":1, "Risk Assessment":1</t>
+          <t>keep:0, "Cybersecurity Evaluation":3</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
@@ -12725,7 +12761,7 @@
         </is>
       </c>
       <c r="Y95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z95" t="b">
         <v>0</v>
@@ -12785,7 +12821,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Engages with CI/CD pipelines using tools.</t>
+          <t>Engages with CI/CD pipelines using tools, in line with dev‑ops practices.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -12915,7 +12951,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Focuses on gender equity principles in IT curricula to ensure leaders' inclusive technology.</t>
+          <t>Focuses on gender equity principles in IT curricula to ensure inclusive technology.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -12959,12 +12995,12 @@
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Gender Equity Education":1</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
@@ -13211,12 +13247,12 @@
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Indigenous Perspective Evaluation":1</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
@@ -13337,12 +13373,12 @@
         <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>0.925</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr">
         <is>
-          <t>keep:2, "Leadership Style Impact Reflection":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
@@ -13540,12 +13576,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Professional Teamwork Collaboration</t>
+          <t>Professional Behaviour Collaboration</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>In hybrid IT teams, professional ethics and behaviours engage.</t>
+          <t>In hybrid IT teams, professional ethics and behaviours are engaged.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -13571,7 +13607,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>IT collaboration; team dynamics; ethical standards; teamwork; professional</t>
+          <t>IT collaboration; team dynamics; ethical standards; teamwork; professional behaviour</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -13586,15 +13622,19 @@
         </is>
       </c>
       <c r="R102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S102" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="T102" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:0, "Professional Behaviour Collaboration/Professional Collaboration":2, "Teamwork Collaboration":1</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -13611,7 +13651,7 @@
         </is>
       </c>
       <c r="Y102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z102" t="b">
         <v>0</v>
@@ -13715,12 +13755,12 @@
         <v>0</v>
       </c>
       <c r="S103" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T103" t="inlineStr"/>
       <c r="U103" t="inlineStr">
         <is>
-          <t>keep:2, "Regulatory Standards Evaluation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
@@ -14075,7 +14115,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>leadership styles; communication practices; conflict management approaches; professional relationships; impact observation</t>
+          <t>leadership styles; impact; communication practices; conflict management approaches; professional relationships</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -14487,7 +14527,7 @@
       <c r="T109" t="inlineStr"/>
       <c r="U109" t="inlineStr">
         <is>
-          <t>keep:2, "Code Tracing Debugging Application":1</t>
+          <t>keep:2, "Code Tracing Debugging":1</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
@@ -14560,7 +14600,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Solution Diagram Communication</t>
+          <t>Solution Structure Communication</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -14591,7 +14631,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>visual communication; solution architecture; UML diagrams; flowcharting; technical documentation</t>
+          <t>solution structures; solution architecture; UML diagrams; flowcharting; technical documentation</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -14606,15 +14646,19 @@
         </is>
       </c>
       <c r="R110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S110" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T110" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>keep:2, "Solution Structure Communication":1</t>
+          <t>keep:0, "Solution Structure Communication":2, "Solution Diagram Development":1</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
@@ -14631,7 +14675,7 @@
         </is>
       </c>
       <c r="Y110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z110" t="b">
         <v>1</v>
@@ -14876,7 +14920,7 @@
       <c r="T112" t="inlineStr"/>
       <c r="U112" t="inlineStr">
         <is>
-          <t>keep:2, "Object-oriented Principles Application Explanation":1</t>
+          <t>keep:2, "Object-Oriented Principles Application":1</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
@@ -15003,7 +15047,7 @@
       <c r="T113" t="inlineStr"/>
       <c r="U113" t="inlineStr">
         <is>
-          <t>keep:2, "Object-oriented Software Development":1</t>
+          <t>keep:1, "Object-oriented Programming Implementation":1, "Object-oriented Programming Development":1</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
@@ -15129,12 +15173,12 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>keep:0, "Code Tracing Debugging/Code Debugging":2, "Code Issue Identification":1</t>
+          <t>keep:0, "Code Debugging/Code Tracing Debugging":3</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
@@ -15369,7 +15413,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>unit testing; object-oriented programming; test automation; test cases; system structures</t>
+          <t>unit testing; object-oriented programming; test automation; test cases; requirements</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -15396,7 +15440,7 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>keep:0, "Program Implementation Testing/Program Testing":3</t>
+          <t>keep:0, "Program Implementation Testing/Program Testing/Object-Oriented Program Testing":3</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
@@ -15596,7 +15640,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Solution Structure Design</t>
+          <t>Solution Structure Development</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -15627,7 +15671,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>technical writing; system diagrams; UML; design; solution structure</t>
+          <t>technical writing; system diagrams; UML; software design; solution structure</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -15654,7 +15698,7 @@
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>keep:0, "Solution Structure Design":2, "Solution Structure Design Evaluation":1</t>
+          <t>keep:0, "Solution Structure Development":2, "Solution Structure Design":1</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
@@ -15678,7 +15722,7 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>Solution Diagram Communication</t>
+          <t>Solution Structure Development</t>
         </is>
       </c>
       <c r="AB118" t="b">
@@ -15784,7 +15828,7 @@
       <c r="T119" t="inlineStr"/>
       <c r="U119" t="inlineStr">
         <is>
-          <t>keep:1, "Authentication Mechanism Utilisation":1, "Authentication Mechanism Acquisition":1</t>
+          <t>keep:2, "Authentication Mechanism Utilisation":1</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
@@ -16273,7 +16317,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>exploitation techniques; authentication mechanisms; Windows registry forensics; digital evidence acquisition; application</t>
+          <t>exploitation techniques; exploitation technique application; authentication mechanisms; Windows registry forensics; digital evidence acquisition</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -16295,12 +16339,12 @@
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>keep:0, "Exploitation Technique Application":2, "Digital Evidence Acquisition":1</t>
+          <t>keep:0, "Exploitation Technique Application":3</t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
@@ -16502,7 +16546,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Forensic Framework Application</t>
+          <t>Forensic Framework Discussion</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -16533,7 +16577,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>computer forensics; forensic analysis tools; computer forensic frameworks; application; evidence collection</t>
+          <t>computer forensics; digital investigation; evidence collection; forensic analysis tools; computer forensic frameworks</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -16548,15 +16592,19 @@
         </is>
       </c>
       <c r="R125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S125" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T125" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>keep:1, "Computer Forensic Framework Application":1, "Forensic Framework Discussion":1</t>
+          <t>keep:0, "Forensic Framework Discussion":3</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
@@ -16573,7 +16621,7 @@
         </is>
       </c>
       <c r="Y125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z125" t="b">
         <v>0</v>
@@ -16754,7 +16802,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Findings Report Development</t>
+          <t>Findings Report Design</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -16800,19 +16848,15 @@
         </is>
       </c>
       <c r="R127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T127" t="inlineStr"/>
       <c r="U127" t="inlineStr">
         <is>
-          <t>keep:0, "Findings Report Development":2, "Findings Report Preparation":1</t>
+          <t>keep:1, "Findings Report Development":1, "Forensic Findings Report Design":1</t>
         </is>
       </c>
       <c r="V127" t="inlineStr">
@@ -16884,7 +16928,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>IT Law Compliance Familiarisation</t>
+          <t>IT Law Familiarisation</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -16930,15 +16974,19 @@
         </is>
       </c>
       <c r="R128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S128" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T128" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>keep:2, "IT Law Familiarisation":1</t>
+          <t>keep:0, "IT Law Familiarisation":3</t>
         </is>
       </c>
       <c r="V128" t="inlineStr">
@@ -17010,7 +17058,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Forensic Findings Communication</t>
+          <t>Investigative Findings Communication</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -17056,19 +17104,15 @@
         </is>
       </c>
       <c r="R129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="T129" t="inlineStr"/>
       <c r="U129" t="inlineStr">
         <is>
-          <t>keep:0, "Forensic Findings Communication/Digital Forensic Communication":2, "Procedures and Findings Communication":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V129" t="inlineStr">
@@ -17140,7 +17184,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>System Log Acquisition</t>
+          <t>System Log Analysis</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -17171,7 +17215,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>log parsing; digital forensics; system log acquisition; incident response; syslog</t>
+          <t>log parsing; digital forensics; SIEM; incident response; syslog</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -17186,19 +17230,15 @@
         </is>
       </c>
       <c r="R130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T130" t="inlineStr"/>
       <c r="U130" t="inlineStr">
         <is>
-          <t>keep:1, "System Log Acquisition":2</t>
+          <t>keep:2, "System Log Evidence Acquisition":1</t>
         </is>
       </c>
       <c r="V130" t="inlineStr">
@@ -17215,7 +17255,7 @@
         </is>
       </c>
       <c r="Y130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z130" t="b">
         <v>0</v>
@@ -17301,7 +17341,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>forensic techniques; data recovery; computer crime; access acquisition; contemporary forensic techniques</t>
+          <t>forensic techniques; data recovery; computer crime; access acquisition; application</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -17324,7 +17364,7 @@
       <c r="T131" t="inlineStr"/>
       <c r="U131" t="inlineStr">
         <is>
-          <t>keep:2, "Forensic Technique Evaluation":1</t>
+          <t>keep:2, "Forensic Technique Utilisation":1</t>
         </is>
       </c>
       <c r="V131" t="inlineStr">
@@ -17341,7 +17381,7 @@
         </is>
       </c>
       <c r="Y131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z131" t="b">
         <v>0</v>
@@ -17428,7 +17468,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>professional capabilities; career planning; employer communication; career aspirations; articulation</t>
+          <t>personal branding; career planning; employer communication; career aspirations; articulation</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -17446,12 +17486,12 @@
         <v>0</v>
       </c>
       <c r="S132" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T132" t="inlineStr"/>
       <c r="U132" t="inlineStr">
         <is>
-          <t>keep:2, "Career Goal Articulation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V132" t="inlineStr">
@@ -17700,12 +17740,12 @@
         <v>0</v>
       </c>
       <c r="S134" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T134" t="inlineStr"/>
       <c r="U134" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Critical Reflection":1</t>
         </is>
       </c>
       <c r="V134" t="inlineStr">
@@ -17832,7 +17872,7 @@
       <c r="T135" t="inlineStr"/>
       <c r="U135" t="inlineStr">
         <is>
-          <t>keep:2, "Professional Capabilities Articulation":1</t>
+          <t>keep:2, "Employer Aspiration Articulation":1</t>
         </is>
       </c>
       <c r="V135" t="inlineStr">
@@ -18110,9 +18150,13 @@
         <v>0</v>
       </c>
       <c r="Z137" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA137" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>Professional Work Execution (LLM verified, sim=0.83)</t>
+        </is>
+      </c>
       <c r="AB137" t="b">
         <v>0</v>
       </c>
@@ -18212,12 +18256,12 @@
         <v>0</v>
       </c>
       <c r="S138" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T138" t="inlineStr"/>
       <c r="U138" t="inlineStr">
         <is>
-          <t>keep:2, "Personal Development Planning":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V138" t="inlineStr">
@@ -18290,7 +18334,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Development Planning</t>
+          <t>Personal Development Planning</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -18321,7 +18365,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>career planning; professional development; development plans; job search strategy; personal development</t>
+          <t>career planning; professional development; goal setting; job search strategy; personal development</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -18336,19 +18380,15 @@
         </is>
       </c>
       <c r="R139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T139" t="inlineStr"/>
       <c r="U139" t="inlineStr">
         <is>
-          <t>keep:0, "Development Planning/Personal‑Professional Development Planning/Personal Professional Development Planning":3</t>
+          <t>keep:1, "Personal Professional Development Planning":1, "Personal-Professional Development Planning":1</t>
         </is>
       </c>
       <c r="V139" t="inlineStr">
@@ -18365,7 +18405,7 @@
         </is>
       </c>
       <c r="Y139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z139" t="b">
         <v>0</v>
@@ -18452,7 +18492,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>personal branding; employer outreach; professional capabilities; relationship building; professional networking</t>
+          <t>personal branding; employer outreach; career aspirations; relationship building; professional networking</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -18556,7 +18596,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Professional Practice Understanding</t>
+          <t>Professional Practice Familiarisation</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -18587,7 +18627,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>competency assessment; reflective practice; industry standards; understanding; professional</t>
+          <t>competency assessment; reflective practice; industry standards; professional; familiarisation</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -18602,15 +18642,19 @@
         </is>
       </c>
       <c r="R141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S141" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T141" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>keep:1, "Professional Practice Learning":1, "Professional Practice Familiarisation":1</t>
+          <t>keep:1, "Professional Practice Familiarisation":2</t>
         </is>
       </c>
       <c r="V141" t="inlineStr">
@@ -18627,7 +18671,7 @@
         </is>
       </c>
       <c r="Y141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z141" t="b">
         <v>0</v>
@@ -18683,7 +18727,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Professional Work Participation</t>
+          <t>Professional Work Execution</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -18714,7 +18758,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>internship; workplace learning; industry placement; professional work experience; participation</t>
+          <t>internship; workplace learning; industry placement; professional work experience; host organization</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -18729,19 +18773,15 @@
         </is>
       </c>
       <c r="R142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T142" t="inlineStr"/>
       <c r="U142" t="inlineStr">
         <is>
-          <t>keep:0, "Professional Work Participation":2, "Professional Work Experience Undertaking":1</t>
+          <t>keep:1, "Work Experience Participation":1, "Professional Work Experience Undertaking":1</t>
         </is>
       </c>
       <c r="V142" t="inlineStr">
@@ -18758,16 +18798,12 @@
         </is>
       </c>
       <c r="Y142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z142" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA142" t="inlineStr">
-        <is>
-          <t>Placement Participation (LLM verified, sim=0.83)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA142" t="inlineStr"/>
       <c r="AB142" t="b">
         <v>0</v>
       </c>
@@ -18867,12 +18903,12 @@
         <v>0</v>
       </c>
       <c r="S143" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T143" t="inlineStr"/>
       <c r="U143" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Reflective Experience Documentation":1</t>
         </is>
       </c>
       <c r="V143" t="inlineStr">
@@ -18994,12 +19030,12 @@
         <v>0</v>
       </c>
       <c r="S144" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T144" t="inlineStr"/>
       <c r="U144" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Anti-reverse Engineering Techniques Implementation":1</t>
         </is>
       </c>
       <c r="V144" t="inlineStr">
@@ -19019,13 +19055,9 @@
         <v>0</v>
       </c>
       <c r="Z144" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA144" t="inlineStr">
-        <is>
-          <t>Anti-reverse Engineering Implementation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA144" t="inlineStr"/>
       <c r="AB144" t="b">
         <v>0</v>
       </c>
@@ -19365,7 +19397,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>utilisation; static analysis; dynamic analysis; reverse engineering; malware analysis tool</t>
+          <t>sandbox; static analysis; dynamic analysis; reverse engineering; malware analysis tool</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -19405,7 +19437,7 @@
         </is>
       </c>
       <c r="Y147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z147" t="b">
         <v>1</v>
@@ -19514,12 +19546,12 @@
         <v>0</v>
       </c>
       <c r="S148" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T148" t="inlineStr"/>
       <c r="U148" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Malware Classification-Reporting Standards Implementation":1</t>
         </is>
       </c>
       <c r="V148" t="inlineStr">
@@ -19596,7 +19628,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Malware Detection Strategy Review</t>
+          <t>Malware Detection Strategy Survey</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -19627,7 +19659,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>malware detection; threat intelligence; static code analysis; dynamic sandboxing; behavioral monitoring</t>
+          <t>malware detection; static code analysis; dynamic sandboxing; behavioural monitoring; survey</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -19642,15 +19674,19 @@
         </is>
       </c>
       <c r="R149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S149" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T149" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>keep:1, "Malware Detection Strategy Survey":1, "Malware Detection Strategy Documentation":1</t>
+          <t>keep:0, "Malware Detection Strategy Survey":2, "Malware Strategy Review":1</t>
         </is>
       </c>
       <c r="V149" t="inlineStr">
@@ -19667,12 +19703,16 @@
         </is>
       </c>
       <c r="Y149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z149" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA149" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>Malware Understanding (LLM verified, sim=0.64)</t>
+        </is>
+      </c>
       <c r="AB149" t="b">
         <v>0</v>
       </c>
@@ -19772,12 +19812,12 @@
         <v>0</v>
       </c>
       <c r="S150" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T150" t="inlineStr"/>
       <c r="U150" t="inlineStr">
         <is>
-          <t>keep:2, "Malware Persistence Detection Implementation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V150" t="inlineStr">
@@ -20026,12 +20066,12 @@
         <v>0</v>
       </c>
       <c r="S152" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:1, "Malware Classification-Reporting Standards Implementation":1, "Malware Classification Reporting Implementation":1</t>
         </is>
       </c>
       <c r="V152" t="inlineStr">
@@ -20135,7 +20175,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>cybersecurity; malware analysis; threat intelligence; reverse engineering; intrusion detection</t>
+          <t>malware understanding; malware analysis; threat intelligence; reverse engineering; intrusion detection</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -20179,20 +20219,20 @@
         </is>
       </c>
       <c r="Y153" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA153" t="inlineStr"/>
+      <c r="AB153" t="b">
         <v>1</v>
       </c>
-      <c r="AA153" t="inlineStr">
-        <is>
-          <t>Malware Detection Strategy Review (LLM verified, sim=0.64)</t>
-        </is>
-      </c>
-      <c r="AB153" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC153" t="inlineStr"/>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>vague skill from course description — "Malware Understanding" uses non-assessable term: {'understanding'}</t>
+        </is>
+      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
@@ -20288,12 +20328,12 @@
         <v>0</v>
       </c>
       <c r="S154" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Anti-reverse Engineering Techniques Implementation":1</t>
         </is>
       </c>
       <c r="V154" t="inlineStr">
@@ -20313,13 +20353,9 @@
         <v>0</v>
       </c>
       <c r="Z154" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA154" t="inlineStr">
-        <is>
-          <t>Anti-reverse Engineering Implementation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA154" t="inlineStr"/>
       <c r="AB154" t="b">
         <v>0</v>
       </c>
@@ -20370,7 +20406,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Response Attribution Reporting</t>
+          <t>Attack Attribution Reporting</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -20401,7 +20437,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>threat intelligence; incident response; malware attribution; attack reporting; mitigation</t>
+          <t>threat intelligence; incident response; MITRE ATT&amp;CK; malware attribution; attack reporting</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -20416,19 +20452,15 @@
         </is>
       </c>
       <c r="R155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S155" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T155" t="inlineStr"/>
       <c r="U155" t="inlineStr">
         <is>
-          <t>keep:0, "Response Attribution Reporting":2, "Incident Reporting":1</t>
+          <t>keep:1, "Attack Response Attribution Reporting":1, "Incident Attribution Reporting":1</t>
         </is>
       </c>
       <c r="V155" t="inlineStr">
@@ -20445,16 +20477,12 @@
         </is>
       </c>
       <c r="Y155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z155" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA155" t="inlineStr">
-        <is>
-          <t>Incident Response Reporting</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA155" t="inlineStr"/>
       <c r="AB155" t="b">
         <v>0</v>
       </c>
@@ -20536,7 +20564,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>network forensics; packet analysis; Wireshark; TCPDump; network forensics tools</t>
+          <t>network forensics; packet analysis; Wireshark; TCPDump; digital evidence</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -20576,7 +20604,7 @@
         </is>
       </c>
       <c r="Y156" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z156" t="b">
         <v>0</v>
@@ -20706,9 +20734,13 @@
         <v>0</v>
       </c>
       <c r="Z157" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA157" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>Attack Attribution Reporting</t>
+        </is>
+      </c>
       <c r="AB157" t="b">
         <v>0</v>
       </c>
@@ -20808,12 +20840,12 @@
         <v>0</v>
       </c>
       <c r="S158" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T158" t="inlineStr"/>
       <c r="U158" t="inlineStr">
         <is>
-          <t>keep:2, "Intrusion Detection System Configuration":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V158" t="inlineStr">
@@ -21062,12 +21094,12 @@
         <v>0</v>
       </c>
       <c r="S160" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T160" t="inlineStr"/>
       <c r="U160" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Network Attack Detection Mitigation":1</t>
         </is>
       </c>
       <c r="V160" t="inlineStr">
@@ -21189,12 +21221,12 @@
         <v>0</v>
       </c>
       <c r="S161" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T161" t="inlineStr"/>
       <c r="U161" t="inlineStr">
         <is>
-          <t>keep:2, "Network Attack Investigation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V161" t="inlineStr">
@@ -21214,9 +21246,13 @@
         <v>0</v>
       </c>
       <c r="Z161" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA161" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>Network Log Recovery Analysis (LLM verified, sim=0.63)</t>
+        </is>
+      </c>
       <c r="AB161" t="b">
         <v>0</v>
       </c>
@@ -21341,13 +21377,9 @@
         <v>0</v>
       </c>
       <c r="Z162" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA162" t="inlineStr">
-        <is>
-          <t>Network Forensic Investigation (LLM verified, sim=0.63)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA162" t="inlineStr"/>
       <c r="AB162" t="b">
         <v>0</v>
       </c>
@@ -21525,7 +21557,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Wireless Traffic Analysis</t>
+          <t>Wireless Network Traffic Analysis</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -21556,7 +21588,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>network forensics; wireless traffic analysis; packet sniffing; Wireshark; common wireless attacks</t>
+          <t>network forensics; wireless traffic analysis; Wireshark; common wireless attacks; network forensics tools</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -21571,15 +21603,19 @@
         </is>
       </c>
       <c r="R164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S164" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T164" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U164" t="inlineStr">
         <is>
-          <t>keep:2, "Wireless Network Traffic Analysis":1</t>
+          <t>keep:1, "Wireless Network Traffic Analysis":2</t>
         </is>
       </c>
       <c r="V164" t="inlineStr">
@@ -21596,12 +21632,16 @@
         </is>
       </c>
       <c r="Y164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z164" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA164" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>Wireless Traffic Analysis</t>
+        </is>
+      </c>
       <c r="AB164" t="b">
         <v>0</v>
       </c>
@@ -21701,12 +21741,12 @@
         <v>0</v>
       </c>
       <c r="S165" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="T165" t="inlineStr"/>
       <c r="U165" t="inlineStr">
         <is>
-          <t>keep:1, "Incident Handling":1, "Simulated Incident Response Reporting":1</t>
+          <t>keep:1, "Incident Response Execution":1, "Incident Handling":1</t>
         </is>
       </c>
       <c r="V165" t="inlineStr">
@@ -21810,7 +21850,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>network forensics; wireless security; packet capture; Wireshark; wireless network traffic</t>
+          <t>network forensics; wireless security; packet capture; Wireshark; wireless traffic</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -21857,13 +21897,9 @@
         <v>1</v>
       </c>
       <c r="Z166" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA166" t="inlineStr">
-        <is>
-          <t>Wireless Traffic Analysis</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA166" t="inlineStr"/>
       <c r="AB166" t="b">
         <v>0</v>
       </c>
@@ -22070,7 +22106,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>career planning; decision-making; goal setting; self-assessment; personal development</t>
+          <t>career planning; goal setting; self-assessment; personal development; decision-making</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -22092,12 +22128,12 @@
       </c>
       <c r="T168" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>keep:1, "Personal Professional Development Decision-making":2</t>
+          <t>keep:0, "Personal Development Decision-Making/Personal Professional Development Decision-Making":3</t>
         </is>
       </c>
       <c r="V168" t="inlineStr">
@@ -22218,12 +22254,12 @@
         <v>0</v>
       </c>
       <c r="S169" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T169" t="inlineStr"/>
       <c r="U169" t="inlineStr">
         <is>
-          <t>keep:2, "IT Competency Documentation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V169" t="inlineStr">
@@ -22295,7 +22331,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Critical Professional Role Reflection</t>
+          <t>Critical Professional Reflection</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -22326,7 +22362,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>critical reflection; reflective practice; role; self‑assessment; metacognition</t>
+          <t>critical reflection; reflective practice; professional ethics; self‑assessment; metacognition</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
@@ -22341,19 +22377,15 @@
         </is>
       </c>
       <c r="R170" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S170" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T170" t="inlineStr"/>
       <c r="U170" t="inlineStr">
         <is>
-          <t>keep:1, "Critical Professional Role Reflection/IT Professional Critical Reflection":2</t>
+          <t>keep:2, "IT Professional Role Reflection":1</t>
         </is>
       </c>
       <c r="V170" t="inlineStr">
@@ -22370,7 +22402,7 @@
         </is>
       </c>
       <c r="Y170" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z170" t="b">
         <v>0</v>
@@ -22425,7 +22457,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Employment Evidence Preparation</t>
+          <t>Employment Evidence Provision</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -22456,7 +22488,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>evidence; employment; application materials; career documentation; recruitment process</t>
+          <t>evidence; employment; application materials; career documentation; provision</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -22471,15 +22503,19 @@
         </is>
       </c>
       <c r="R171" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S171" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T171" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t>keep:2, "Employment Evidence Provision":1</t>
+          <t>keep:1, "Employment Evidence Provision":2</t>
         </is>
       </c>
       <c r="V171" t="inlineStr">
@@ -22496,7 +22532,7 @@
         </is>
       </c>
       <c r="Y171" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z171" t="b">
         <v>0</v>
@@ -22582,7 +22618,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>IT ethics; professional conduct; efficient work practices; work practice; demonstration</t>
+          <t>IT ethics; professional conduct; work practice; demonstration; efficient work practices</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -22681,7 +22717,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Course Graduate Outcomes Demonstration</t>
+          <t>Graduate Outcomes Demonstration</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -22712,7 +22748,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>course; curriculum mapping; learning outcomes assessment; competency-based education; graduate</t>
+          <t>curriculum mapping; learning outcomes assessment; competency-based education; demonstration; graduate</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
@@ -22727,19 +22763,15 @@
         </is>
       </c>
       <c r="R173" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S173" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="T173" t="inlineStr"/>
       <c r="U173" t="inlineStr">
         <is>
-          <t>keep:0, "Course Graduate Outcomes Demonstration/Graduate Learning Outcomes Demonstration":3</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V173" t="inlineStr">
@@ -22756,7 +22788,7 @@
         </is>
       </c>
       <c r="Y173" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z173" t="b">
         <v>0</v>
@@ -22968,7 +23000,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>internship; work-based learning; professional placement; participation; career readiness</t>
+          <t>internship; work-based learning; professional placement; experience; career readiness</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -23008,7 +23040,7 @@
         </is>
       </c>
       <c r="Y175" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z175" t="b">
         <v>0</v>
@@ -23063,12 +23095,12 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Study Work Integration</t>
+          <t>Workplace Integration</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Integrates academic learning with workplace tasks for university education and industry needs.</t>
+          <t>Integrates academic learning with workplace tasks to align university education and industry needs.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -23094,7 +23126,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>work‑integrated learning; experiential education; career readiness; applied professional practice; study integration</t>
+          <t>work‑integrated learning; experiential education; industry partnership; career readiness; applied professional practice</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -23109,19 +23141,15 @@
         </is>
       </c>
       <c r="R176" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S176" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T176" t="inlineStr"/>
       <c r="U176" t="inlineStr">
         <is>
-          <t>keep:0, "Study and Work Integration/Study Work Integration":3</t>
+          <t>keep:0, "Study-Work Integration":1, "Study Work Integration":1, "Education Workplace Integration":1</t>
         </is>
       </c>
       <c r="V176" t="inlineStr">
@@ -23138,7 +23166,7 @@
         </is>
       </c>
       <c r="Y176" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z176" t="b">
         <v>1</v>
@@ -23246,12 +23274,12 @@
         <v>0</v>
       </c>
       <c r="S177" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T177" t="inlineStr"/>
       <c r="U177" t="inlineStr">
         <is>
-          <t>keep:2, "IT Competency Documentation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V177" t="inlineStr">
@@ -23323,7 +23351,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Work-life Balance Decision-making</t>
+          <t>Work-life Balance Appreciation</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -23354,7 +23382,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>professional development; time management; personal development; decision-making; work-life balance</t>
+          <t>wellbeing; personal development; work-life balance; professional development; appreciation</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -23369,19 +23397,15 @@
         </is>
       </c>
       <c r="R178" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S178" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="T178" t="inlineStr"/>
       <c r="U178" t="inlineStr">
         <is>
-          <t>keep:1, "Work-life Balance Decision-Making":2</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V178" t="inlineStr">
@@ -23405,9 +23429,13 @@
       </c>
       <c r="AA178" t="inlineStr"/>
       <c r="AB178" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC178" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>vague skill from course description — "Work-life Balance Appreciation" uses non-assessable term: {'appreciation'}</t>
+        </is>
+      </c>
       <c r="AD178" t="b">
         <v>0</v>
       </c>
@@ -23485,7 +23513,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>scrum; kanban; sprint planning; backlog management; agile project management</t>
+          <t>agile; scrum; kanban; sprint planning; backlog management</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -23655,13 +23683,9 @@
         <v>0</v>
       </c>
       <c r="Z180" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA180" t="inlineStr">
-        <is>
-          <t>Problem Solving</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA180" t="inlineStr"/>
       <c r="AB180" t="b">
         <v>0</v>
       </c>
@@ -23844,7 +23868,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Applies modern IT tools and techniques to functional solutions for real-world projects.</t>
+          <t>Applies modern IT tools and techniques in real-world projects.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -24040,13 +24064,9 @@
         <v>0</v>
       </c>
       <c r="Z183" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA183" t="inlineStr">
-        <is>
-          <t>Problem Solving</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA183" t="inlineStr"/>
       <c r="AB183" t="b">
         <v>0</v>
       </c>
@@ -24413,7 +24433,7 @@
       <c r="T186" t="inlineStr"/>
       <c r="U186" t="inlineStr">
         <is>
-          <t>keep:2, "Project Progress Productivity Monitoring":1</t>
+          <t>keep:2, "Project Monitoring":1</t>
         </is>
       </c>
       <c r="V186" t="inlineStr">
@@ -24486,7 +24506,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Requirements Analysis</t>
+          <t>Requirement Analysis</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -24517,7 +24537,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>requirements elicitation; use case modeling; functional specification; requirement analysis; design solutions</t>
+          <t>business analysis; requirements elicitation; use case modeling; functional specification; requirement analysis</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -24532,19 +24552,15 @@
         </is>
       </c>
       <c r="R187" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S187" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T187" t="inlineStr"/>
       <c r="U187" t="inlineStr">
         <is>
-          <t>keep:1, "Requirements Analysis":2</t>
+          <t>keep:2, "Requirements Analysis":1</t>
         </is>
       </c>
       <c r="V187" t="inlineStr">
@@ -24561,16 +24577,12 @@
         </is>
       </c>
       <c r="Y187" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z187" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA187" t="inlineStr">
-        <is>
-          <t>Solution Design</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA187" t="inlineStr"/>
       <c r="AB187" t="b">
         <v>0</v>
       </c>
@@ -24822,9 +24834,13 @@
         <v>0</v>
       </c>
       <c r="Z189" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA189" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>Requirement Analysis</t>
+        </is>
+      </c>
       <c r="AB189" t="b">
         <v>0</v>
       </c>
@@ -24875,7 +24891,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Sprint Project Outcome Reflection</t>
+          <t>Sprint Outcome Reflection</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -24906,7 +24922,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>agile; sprint retrospective; project performance metrics; outcome analysis; continuous improvement</t>
+          <t>agile; sprint retrospective; project performance metrics; outcome analysis; reflection</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -24921,36 +24937,32 @@
         </is>
       </c>
       <c r="R190" t="b">
+        <v>0</v>
+      </c>
+      <c r="S190" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="T190" t="inlineStr"/>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>keep:1, "Sprint Project Outcomes Reflection":1, "Sprint-Project Outcome Reflection":1</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>Reflects on sprint and project results in hybrid settings, considering outcomes to inform improvements.</t>
+        </is>
+      </c>
+      <c r="W190" t="b">
+        <v>0</v>
+      </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>agile, sprint retrospective, project performance metrics, outcome analysis, continuous improvement</t>
+        </is>
+      </c>
+      <c r="Y190" t="b">
         <v>1</v>
-      </c>
-      <c r="S190" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
-      <c r="U190" t="inlineStr">
-        <is>
-          <t>keep:1, "Sprint Project Outcome Reflection/Outcome Reflection":2</t>
-        </is>
-      </c>
-      <c r="V190" t="inlineStr">
-        <is>
-          <t>Reflects on sprint and project results in hybrid settings, considering outcomes to inform improvements.</t>
-        </is>
-      </c>
-      <c r="W190" t="b">
-        <v>0</v>
-      </c>
-      <c r="X190" t="inlineStr">
-        <is>
-          <t>agile, sprint retrospective, project performance metrics, outcome analysis, continuous improvement</t>
-        </is>
-      </c>
-      <c r="Y190" t="b">
-        <v>0</v>
       </c>
       <c r="Z190" t="b">
         <v>0</v>
@@ -25260,7 +25272,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Time and Process Management</t>
+          <t>Time Management</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -25291,7 +25303,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>time; processes; prioritization; scheduling; task planning</t>
+          <t>time; prioritization; scheduling; task planning; self‑regulation</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -25306,19 +25318,15 @@
         </is>
       </c>
       <c r="R193" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S193" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T193" t="inlineStr"/>
       <c r="U193" t="inlineStr">
         <is>
-          <t>keep:1, "Time and Process Management":2</t>
+          <t>keep:1, "Time and Process Management":1, "Time-Process Management":1</t>
         </is>
       </c>
       <c r="V193" t="inlineStr">
@@ -25335,7 +25343,7 @@
         </is>
       </c>
       <c r="Y193" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z193" t="b">
         <v>0</v>
@@ -25440,12 +25448,12 @@
         <v>0</v>
       </c>
       <c r="S194" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T194" t="inlineStr"/>
       <c r="U194" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Learning Transfer Communication":1</t>
         </is>
       </c>
       <c r="V194" t="inlineStr">
@@ -25551,7 +25559,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>agile; project management; scrum; sprint planning; iterative development</t>
+          <t>agile; project management; application; sprint planning; iterative development</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -25591,7 +25599,7 @@
         </is>
       </c>
       <c r="Y195" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z195" t="b">
         <v>0</v>
@@ -25703,7 +25711,7 @@
       <c r="T196" t="inlineStr"/>
       <c r="U196" t="inlineStr">
         <is>
-          <t>keep:2, "Problem Solving Application":1</t>
+          <t>keep:2, "Critical Thinking Problem-Solving Application":1</t>
         </is>
       </c>
       <c r="V196" t="inlineStr">
@@ -25907,7 +25915,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Design Development Strategy Formulation</t>
+          <t>Design Strategy Formulation</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -25938,7 +25946,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>design thinking; strategic planning; design roadmap; development strategies; design strategies</t>
+          <t>design thinking; strategic planning; innovation management; design roadmap; development strategies</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
@@ -25953,19 +25961,15 @@
         </is>
       </c>
       <c r="R198" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S198" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T198" t="inlineStr"/>
       <c r="U198" t="inlineStr">
         <is>
-          <t>keep:0, "Design Development Strategy Formulation":2, "Design-Development Strategy Formulation":1</t>
+          <t>keep:2, "Design-Development Strategy Formulation":1</t>
         </is>
       </c>
       <c r="V198" t="inlineStr">
@@ -25982,7 +25986,7 @@
         </is>
       </c>
       <c r="Y198" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z198" t="b">
         <v>0</v>
@@ -26360,7 +26364,7 @@
       </c>
       <c r="U201" t="inlineStr">
         <is>
-          <t>keep:0, "IT Professional Practice Application":3</t>
+          <t>keep:0, "Professional Practice Application/IT Professional Practice Application":3</t>
         </is>
       </c>
       <c r="V201" t="inlineStr">
@@ -26470,7 +26474,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>performance metrics; key performance indicators; stakeholder reporting; project; demonstration</t>
+          <t>project; demonstration; performance metrics; key performance indicators; outcome</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
@@ -26492,12 +26496,12 @@
       </c>
       <c r="T202" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U202" t="inlineStr">
         <is>
-          <t>keep:0, "Project Outcome Demonstration":3</t>
+          <t>keep:1, "Project Outcome Demonstration":2</t>
         </is>
       </c>
       <c r="V202" t="inlineStr">
@@ -26572,7 +26576,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Project Schedule Planning</t>
+          <t>Project Deliverable Scheduling</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -26603,7 +26607,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>Gantt chart; critical path method; project timeline; deliverable tracking; schedule</t>
+          <t>Gantt chart; critical path method; project timeline; deliverable tracking; scheduling</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
@@ -26618,15 +26622,19 @@
         </is>
       </c>
       <c r="R203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S203" t="n">
-        <v>0</v>
-      </c>
-      <c r="T203" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t>keep:0, "Project Deliverable Scheduling":1, "Project Deliverable Management":1, "Project Deliverable Planning":1</t>
+          <t>keep:0, "Project Deliverable Scheduling":3</t>
         </is>
       </c>
       <c r="V203" t="inlineStr">
@@ -26750,7 +26758,7 @@
         <v>0</v>
       </c>
       <c r="S204" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T204" t="inlineStr"/>
       <c r="U204" t="inlineStr">
@@ -26775,9 +26783,13 @@
         <v>0</v>
       </c>
       <c r="Z204" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA204" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>Time Management (LLM verified, sim=0.69)</t>
+        </is>
+      </c>
       <c r="AB204" t="b">
         <v>0</v>
       </c>
@@ -26959,7 +26971,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Stakeholder Needs Analysis</t>
+          <t>Project Requirements Analysis</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -26990,7 +27002,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>requirements gathering; needs analysis; project scheduling; capability assessment; business analysis</t>
+          <t>requirements gathering; needs analysis; project scheduling; capability assessment; project deliverables</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
@@ -27005,15 +27017,19 @@
         </is>
       </c>
       <c r="R206" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S206" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T206" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/3: </t>
+        </is>
+      </c>
       <c r="U206" t="inlineStr">
         <is>
-          <t>keep:2, "Stakeholder and Project Analysis":1</t>
+          <t>keep:0, "Project Requirements Analysis":3</t>
         </is>
       </c>
       <c r="V206" t="inlineStr">
@@ -27030,7 +27046,7 @@
         </is>
       </c>
       <c r="Y206" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z206" t="b">
         <v>0</v>
@@ -27119,7 +27135,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>student mentorship; team leadership; peer coaching; hybrid learning environment; project guidance</t>
+          <t>student mentorship; team leadership; peer coaching; project guidance; team mentoring</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -27137,12 +27153,12 @@
         <v>0</v>
       </c>
       <c r="S207" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="T207" t="inlineStr"/>
       <c r="U207" t="inlineStr">
         <is>
-          <t>keep:3</t>
+          <t>keep:2, "Student Mentoring":1</t>
         </is>
       </c>
       <c r="V207" t="inlineStr">
@@ -27159,7 +27175,7 @@
         </is>
       </c>
       <c r="Y207" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z207" t="b">
         <v>0</v>
@@ -27404,7 +27420,7 @@
       </c>
       <c r="U209" t="inlineStr">
         <is>
-          <t>keep:0, "Information Technology Application":3</t>
+          <t>keep:0, "Information Technology Application/Technology Application/Information Technology Methods Application":3</t>
         </is>
       </c>
       <c r="V209" t="inlineStr">
@@ -27528,12 +27544,12 @@
         <v>0</v>
       </c>
       <c r="S210" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T210" t="inlineStr"/>
       <c r="U210" t="inlineStr">
         <is>
-          <t>keep:2, "Skill Transfer Demonstration":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V210" t="inlineStr">
@@ -27762,7 +27778,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>defensive security; cybersecurity; threat modeling; incident response; security operations</t>
+          <t>defensive security; threat modeling; incident response; security operations; security synthesis</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -27780,12 +27796,12 @@
         <v>0</v>
       </c>
       <c r="S212" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T212" t="inlineStr"/>
       <c r="U212" t="inlineStr">
         <is>
-          <t>keep:2, "Defensive Security Knowledge Integration":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V212" t="inlineStr">
@@ -27802,7 +27818,7 @@
         </is>
       </c>
       <c r="Y212" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z212" t="b">
         <v>0</v>
@@ -27857,7 +27873,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Ethical Constraints Identification</t>
+          <t>Ethical Compliance Recognition</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -27888,7 +27904,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>ethics; legal regulations; compliance; constraints; code of conduct</t>
+          <t>ethics; legal regulations; compliance; recognition; code of conduct</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
@@ -27903,19 +27919,15 @@
         </is>
       </c>
       <c r="R213" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S213" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="T213" t="inlineStr"/>
       <c r="U213" t="inlineStr">
         <is>
-          <t>keep:0, "Ethical Constraints Identification/Ethical Compliance Identification":2, "Ethical Legal Constraints Recognition":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V213" t="inlineStr">
@@ -27932,7 +27944,7 @@
         </is>
       </c>
       <c r="Y213" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z213" t="b">
         <v>0</v>
@@ -28036,12 +28048,12 @@
         <v>0</v>
       </c>
       <c r="S214" t="n">
-        <v>0.925</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="T214" t="inlineStr"/>
       <c r="U214" t="inlineStr">
         <is>
-          <t>keep:2, "Security Vulnerability Exploitation":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V214" t="inlineStr">
@@ -28113,7 +28125,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Security Vulnerability Exploitation</t>
+          <t>Vulnerability Exploitation</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -28159,19 +28171,15 @@
         </is>
       </c>
       <c r="R215" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S215" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T215" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.9499999999999998</v>
+      </c>
+      <c r="T215" t="inlineStr"/>
       <c r="U215" t="inlineStr">
         <is>
-          <t>keep:0, "Security Vulnerability Exploitation":3</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V215" t="inlineStr">
@@ -28191,13 +28199,9 @@
         <v>1</v>
       </c>
       <c r="Z215" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA215" t="inlineStr">
-        <is>
-          <t>Penetration Testing Execution (LLM verified, sim=0.68)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA215" t="inlineStr"/>
       <c r="AB215" t="b">
         <v>0</v>
       </c>
@@ -28373,7 +28377,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Penetration Testing Execution</t>
+          <t>Penetration Testing</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -28404,7 +28408,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>execution; ethical hacking; Metasploit; Kali Linux; penetration testing</t>
+          <t>ethical hacking; exploit development; Metasploit; Kali Linux; penetration testing</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -28419,15 +28423,19 @@
         </is>
       </c>
       <c r="R217" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S217" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T217" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U217" t="inlineStr">
         <is>
-          <t>keep:2, "Penetration Testing":1</t>
+          <t>keep:0, "Penetration Testing":2, "Penetration Testing Implementation":1</t>
         </is>
       </c>
       <c r="V217" t="inlineStr">
@@ -28444,12 +28452,16 @@
         </is>
       </c>
       <c r="Y217" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z217" t="b">
         <v>1</v>
       </c>
-      <c r="Z217" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA217" t="inlineStr"/>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>Ethical Hacking Problem Solving (LLM verified, sim=0.71)</t>
+        </is>
+      </c>
       <c r="AB217" t="b">
         <v>0</v>
       </c>
@@ -28630,7 +28642,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Writes clear technical documents and presentations, speaking to translate complex concepts for academic audiences.</t>
+          <t>Writes clear technical documents and speaks in presentations to convey complex concepts to academic audiences.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -28812,12 +28824,12 @@
       </c>
       <c r="T220" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 2/3: </t>
+          <t xml:space="preserve">consensus 3/3: </t>
         </is>
       </c>
       <c r="U220" t="inlineStr">
         <is>
-          <t>keep:1, "Data Analytics Solution Implementation":2</t>
+          <t>keep:0, "Data Analytics Solution Implementation":3</t>
         </is>
       </c>
       <c r="V220" t="inlineStr">
@@ -28893,7 +28905,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Data Analytics Application</t>
+          <t>Data Analytics Modelling</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -28924,7 +28936,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>supervised learning; unsupervised learning; regression analysis; clustering algorithms; classification modelling</t>
+          <t>supervised learning; regression analysis; clustering algorithms; classification modelling; data analytics</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
@@ -28946,12 +28958,12 @@
       </c>
       <c r="T221" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U221" t="inlineStr">
         <is>
-          <t>keep:0, "Data Analytics Application":3</t>
+          <t>keep:1, "Data Analytics Modelling":2</t>
         </is>
       </c>
       <c r="V221" t="inlineStr">
@@ -28968,14 +28980,14 @@
         </is>
       </c>
       <c r="Y221" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z221" t="b">
         <v>1</v>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>Clustering Analysis</t>
+          <t>Data Analytics Application</t>
         </is>
       </c>
       <c r="AB221" t="b">
@@ -29027,7 +29039,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Clustering Analysis</t>
+          <t>Data Analytics Application</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -29058,7 +29070,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>clustering; unsupervised learning; data mining; pattern recognition; machine learning algorithms</t>
+          <t>clustering; unsupervised learning; machine learning algorithms; analytics; application</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
@@ -29073,15 +29085,19 @@
         </is>
       </c>
       <c r="R222" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S222" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T222" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>keep:1, "Clustering Technique Application":1, "Data Analytics Application":1</t>
+          <t>keep:1, "Data Analytics Application":2</t>
         </is>
       </c>
       <c r="V222" t="inlineStr">
@@ -29098,12 +29114,16 @@
         </is>
       </c>
       <c r="Y222" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z222" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA222" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>Data Analytics Application</t>
+        </is>
+      </c>
       <c r="AB222" t="b">
         <v>0</v>
       </c>
@@ -29184,7 +29204,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>data analytics; evidence-based evaluation; quantitative analysis; data visualization; data analytics principles</t>
+          <t>data analytics; quantitative analysis; data visualization; data analytics principles; data analytics application</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
@@ -29228,14 +29248,14 @@
         </is>
       </c>
       <c r="Y223" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z223" t="b">
         <v>1</v>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>Evidence Evaluation (LLM verified, sim=0.73)</t>
+          <t>Data Analytics Application</t>
         </is>
       </c>
       <c r="AB223" t="b">
@@ -29365,7 +29385,7 @@
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>Python Scripting Implementation (LLM verified, sim=0.66)</t>
+          <t>Cyber Security Data Processing</t>
         </is>
       </c>
       <c r="AB224" t="b">
@@ -29417,7 +29437,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Cyber Security Data Analysis</t>
+          <t>Cyber Security Data Processing</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -29448,7 +29468,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>threat intelligence; SIEM; log analysis; network traffic analytics; cyber security data</t>
+          <t>threat intelligence; SIEM; log analysis; network traffic analytics; processing</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
@@ -29463,19 +29483,15 @@
         </is>
       </c>
       <c r="R225" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S225" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T225" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 3/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T225" t="inlineStr"/>
       <c r="U225" t="inlineStr">
         <is>
-          <t>keep:0, "Cyber Security Data Analysis":3</t>
+          <t>keep:2, "Cyber Security Data Analysis":1</t>
         </is>
       </c>
       <c r="V225" t="inlineStr">
@@ -29492,16 +29508,12 @@
         </is>
       </c>
       <c r="Y225" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z225" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA225" t="inlineStr">
-        <is>
-          <t>Cyber Security Data Analysis</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA225" t="inlineStr"/>
       <c r="AB225" t="b">
         <v>0</v>
       </c>
@@ -29629,7 +29641,7 @@
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>Python Scripting Implementation (LLM verified, sim=0.66)</t>
+          <t>Cyber Security Data Processing</t>
         </is>
       </c>
       <c r="AB226" t="b">
@@ -29755,9 +29767,13 @@
         <v>0</v>
       </c>
       <c r="Z227" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA227" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>Cyber Security Data Processing (LLM verified, sim=0.73)</t>
+        </is>
+      </c>
       <c r="AB227" t="b">
         <v>0</v>
       </c>
@@ -29881,9 +29897,13 @@
         <v>0</v>
       </c>
       <c r="Z228" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA228" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>Cyber Security Data Processing (LLM verified, sim=0.63)</t>
+        </is>
+      </c>
       <c r="AB228" t="b">
         <v>0</v>
       </c>
@@ -30090,7 +30110,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>data analytics; clustering techniques; regression analysis; supervised learning; unsupervised learning</t>
+          <t>analytics; clustering techniques; regression analysis; supervised learning; unsupervised learning</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
@@ -30141,7 +30161,7 @@
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>Clustering Analysis</t>
+          <t>Regression Modelling</t>
         </is>
       </c>
       <c r="AB230" t="b">
@@ -30267,9 +30287,13 @@
         <v>0</v>
       </c>
       <c r="Z231" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA231" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>Cyber Security Data Processing (LLM verified, sim=0.66)</t>
+        </is>
+      </c>
       <c r="AB231" t="b">
         <v>0</v>
       </c>
@@ -30319,7 +30343,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Data Analytics Application</t>
+          <t>Regression Modelling</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -30350,7 +30374,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>supervised learning; statistical modeling; machine learning; regression; unsupervised learning</t>
+          <t>supervised learning; predictive analytics; statistical modeling; machine learning; regression</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
@@ -30365,19 +30389,15 @@
         </is>
       </c>
       <c r="R232" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S232" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T232" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 2/3: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="T232" t="inlineStr"/>
       <c r="U232" t="inlineStr">
         <is>
-          <t>keep:1, "Data Analytics Application":2</t>
+          <t>keep:1, "Data Analytics Modelling":1, "Data Analytics Application":1</t>
         </is>
       </c>
       <c r="V232" t="inlineStr">
@@ -30394,16 +30414,12 @@
         </is>
       </c>
       <c r="Y232" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z232" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA232" t="inlineStr">
-        <is>
-          <t>Clustering Analysis</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA232" t="inlineStr"/>
       <c r="AB232" t="b">
         <v>0</v>
       </c>
@@ -30502,12 +30518,12 @@
         <v>0</v>
       </c>
       <c r="S233" t="n">
-        <v>0.95</v>
+        <v>0.9499999999999998</v>
       </c>
       <c r="T233" t="inlineStr"/>
       <c r="U233" t="inlineStr">
         <is>
-          <t>keep:2, "Data Analytics Methodology Learning":1</t>
+          <t>keep:3</t>
         </is>
       </c>
       <c r="V233" t="inlineStr">
@@ -30703,7 +30719,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Online Unit Completion</t>
+          <t>Unit Completion</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -30749,15 +30765,19 @@
         </is>
       </c>
       <c r="R235" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S235" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T235" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U235" t="inlineStr">
         <is>
-          <t>keep:2, "Introductory Unit Completion":1</t>
+          <t>keep:1, "Unit Completion/Introductory Unit Completion":2</t>
         </is>
       </c>
       <c r="V235" t="inlineStr">
@@ -30777,9 +30797,13 @@
         <v>0</v>
       </c>
       <c r="Z235" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA235" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>Online Unit Completion (LLM verified, sim=0.70)</t>
+        </is>
+      </c>
       <c r="AB235" t="b">
         <v>0</v>
       </c>
@@ -30881,7 +30905,7 @@
       <c r="T236" t="inlineStr"/>
       <c r="U236" t="inlineStr">
         <is>
-          <t>keep:1, "Career Education Journey Development":1, "Career Education Demonstration":1</t>
+          <t>keep:1, "Career Education Journey Demonstration":1, "Career Education Progression":1</t>
         </is>
       </c>
       <c r="V236" t="inlineStr">
@@ -30951,7 +30975,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Career Tool Development</t>
+          <t>Personalised Career Tool Development</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -30982,7 +31006,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>career development; personal branding; employability enhancement; skill assessment tools; career tools</t>
+          <t>career development; employability enhancement; skill assessment tools; career tools; personalised career tools</t>
         </is>
       </c>
       <c r="O237" t="inlineStr">
@@ -30997,15 +31021,19 @@
         </is>
       </c>
       <c r="R237" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S237" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T237" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 2/3: </t>
+        </is>
+      </c>
       <c r="U237" t="inlineStr">
         <is>
-          <t>keep:2, "Career Tool Creation":1</t>
+          <t>keep:0, "Personalised Career Tool Development":2, "Career Tool Creation":1</t>
         </is>
       </c>
       <c r="V237" t="inlineStr">
@@ -31022,7 +31050,7 @@
         </is>
       </c>
       <c r="Y237" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z237" t="b">
         <v>0</v>
@@ -31149,13 +31177,9 @@
         <v>0</v>
       </c>
       <c r="Z238" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA238" t="inlineStr">
-        <is>
-          <t>Career Tool Development (LLM verified, sim=0.73)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA238" t="inlineStr"/>
       <c r="AB238" t="b">
         <v>0</v>
       </c>
@@ -31354,7 +31378,7 @@
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>e‑learning; learning management system; completion; self‑paced online instruction; unit</t>
+          <t>e‑learning; learning management system; completion; unit; self‑paced online instruction</t>
         </is>
       </c>
       <c r="O240" t="inlineStr">
@@ -31376,12 +31400,12 @@
       </c>
       <c r="T240" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>keep:0, "Online Unit Completion":3</t>
+          <t>keep:1, "Online Unit Completion":2</t>
         </is>
       </c>
       <c r="V240" t="inlineStr">
@@ -31401,13 +31425,9 @@
         <v>1</v>
       </c>
       <c r="Z240" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA240" t="inlineStr">
-        <is>
-          <t>Online Unit Completion</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA240" t="inlineStr"/>
       <c r="AB240" t="b">
         <v>0</v>
       </c>
@@ -31508,12 +31528,12 @@
       </c>
       <c r="T241" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 3/3: </t>
+          <t xml:space="preserve">consensus 2/3: </t>
         </is>
       </c>
       <c r="U241" t="inlineStr">
         <is>
-          <t>keep:0, "Career Education Development":3</t>
+          <t>keep:1, "Career Education Development":2</t>
         </is>
       </c>
       <c r="V241" t="inlineStr">
